--- a/PubMed_resultsx.xlsx
+++ b/PubMed_resultsx.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,338 +461,334 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>41937591</t>
+          <t>41866518</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Effectiveness of the McKenzie-based exercises in improving pain, disability, and cervical range of motion in patients with chronic non-specific neck pain: A systematic review with meta-analysis.</t>
+          <t>Mobilization with movement enhances early rehabilitation outcomes in knee osteoarthritis: a six-week randomized controlled trial.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The McKenzie Method is widely used in managing spinal pain; however, its effectiveness in chronic nonspecific neck pain (CNNP) remains uncertain. To assess the effectiveness of the McKenzie Method compared to placebo, usual care, or other interventions in reducing pain, disability, and improving the cervical range of motion (CROM) in patients with CNNP. A systematic review with meta-analysis was conducted in PubMed Medline, Scopus, Web of Science, CINAHL Complete, CENTRAL and PEDro up to July 2025. Randomized controlled trials including adults with CNNP treated with the McKenzie Method were analyzed. Random-effects meta-analyses calculated standardized mean difference (SMD) with 95% confidence intervals (95% CI). Heterogeneity (I&lt;sup&gt;2&lt;/sup&gt;), sensitivityanalyses, publication bias, and certainty of evidence (GRADE) were assessed. Eight studies (389 participants) were included. Low-quality evidence showed a large effect favoring the McKenzie Method for pain reduction (SMD =-0.57; 95% CI: -1.1 to -0.04; &lt;i&gt;p&lt;/i&gt; = .034; I&lt;sup&gt;2&lt;/sup&gt; = 31.5%) and disability (SMD =-0.43; 95% CI: -0.90 to -0.01; &lt;i&gt;p&lt;/i&gt; = .047; I&lt;sup&gt;2&lt;/sup&gt; = 19.5%). Publication bias was detected for disability, with trim-and-fill suggesting the true effect may be larger. Significant improvements in active CROM were observed for extension, flexion, and rotation, whereas no significant improvement was found for lateral flexion. No evidence of publication bias or sensitivity effects was found for these outcomes. In adults with CNNP, interventions described as the McKenzie Method were associated with small improvements in pain, disability, and cervical flexion, extension, and rotation, with no clear effect on lateral flexion. Effects are short-term and of low certainty. Evidence for medium or long-term outcomes has not been reported based on studies retained in this review.</t>
+          <t>Exercise is a first-line approach for knee osteoarthritis (KOA), yet pain during movement may limit adherence. Mulligan’s mobilization with movement (MWM) is proposed to facilitate pain-free exercise and hasten early clinical gains. To determine whether adding MWM to isometric training (IT) improves pain, quadriceps strength, and disability over six weeks compared with IT alone. Two-arm, double-masked RCT in adults with radiographic KOA (Kellgren–Lawrence grade 2–3). Participants were randomized to MWM + IT or IT-only (&lt;i&gt;n&lt;/i&gt; = 25/group), 5 supervised sessions/week for 6 weeks. Outcomes: pain (VAS), quadriceps strength (strain-gauge dynamometry), disability (WOMAC) measured at baseline, weeks 1, 3, and 6. Primary analyses used linear mixed-effects models with fixed effects for Group, Time, and Group × Time and a random intercept for Subject; joint Wald tests evaluated factor significance. Significant Time effects indicated improvement across outcomes (VAS χ&lt;sup&gt;2&lt;/sup&gt;(3) = 456.338, &lt;i&gt;p&lt;/i&gt; &lt; 0.0001; STN χ&lt;sup&gt;2&lt;/sup&gt;(3) = 186.876, &lt;i&gt;p&lt;/i&gt; &lt; 0.0001; WOMAC χ&lt;sup&gt;2&lt;/sup&gt;(3) = 1515.459, &lt;i&gt;p&lt;/i&gt; &lt; 0.0001). Group×Time interactions were significant for VAS (χ&lt;sup&gt;2&lt;/sup&gt;(3) = 170.550, &lt;i&gt;p&lt;/i&gt; &lt; 0.0001), STN (χ&lt;sup&gt;2&lt;/sup&gt;(3) = 204.327, &lt;i&gt;p&lt;/i&gt; &lt; 0.0001), and WOMAC (χ&lt;sup&gt;2&lt;/sup&gt;(3) = 71.041, &lt;i&gt;p&lt;/i&gt; &lt; 0.0001), demonstrating faster and larger six-week gains with MWM + IT. The Group main effect was significant for VAS (χ&lt;sup&gt;2&lt;/sup&gt;(1) = 42.599, &lt;i&gt;p&lt;/i&gt; &lt; 0.0001) and non-significant for STN (χ&lt;sup&gt;2&lt;/sup&gt;(1) = 0.613, &lt;i&gt;p&lt;/i&gt; = 0.4336) and WOMAC (χ&lt;sup&gt;2&lt;/sup&gt;(1) = 0.019, &lt;i&gt;p&lt;/i&gt; = 0.8901). Adding MWM to IT accelerated and amplified six-week improvements in pain, strength, and function compared with IT alone. Early integration of MWM may enhance pain-free exercise and short-term rehabilitation outcomes in KOA. Larger multicentre trials with extended follow-up and economic evaluation are warranted. ClinicalTrials.gov Identifier: NCT05577403; prospectively registered on 12 /07/2021 (last updated on 14/09/2025).; available at https://clinicaltrials.gov/study/NCT05577403.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>García-López Héctor, Morales-Quintana Álvaro, Obrero-Gaitán Esteban, Romero-Del Rey Raúl, Cortés-Pérez Irene</t>
+          <t>Hasan Shahnaz, Iqbal Amir, Ibrahim Abeer Ramadan, Diab Reham H, Iqbal Zaheen A, Hasan Tabinda, Anwer Shahnawaz, Alghadir Ahmad H</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Physiotherapy theory and practice</t>
+          <t>Chiropractic &amp; manual therapies</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pubmed/41937591</t>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/41866518</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>41827107</t>
+          <t>41862863</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Effectiveness of Different Exercise-Based Interventions Combined or Not with Electrotherapy Versus McKenzie Method Alone for Nonspecific Chronic Neck Pain: A Systematic Review and Meta-Analysis.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Background/Objectives:&lt;/b&gt; Chronic nonspecific neck pain is a common global health problem that diminishes people's quality of life and functionality. Strengthening and mobility exercises are a fundamental tool in managing this condition. Combined treatment with electrotherapy appears to have promising results; however, the evidence is limited. The aim of this review was to compare the effectiveness of therapeutic exercise combined with electrotherapy versus the McKenzie method alone in improving pain and disability in adults. &lt;b&gt;Methods:&lt;/b&gt; A systematic review and meta-analysis of randomized clinical trials was conducted following the PRISMA guidelines. Studies published up to June 2025 were extracted from major scientific databases. High-quality studies evaluating therapeutic exercise with or without electrostimulation and studies evaluating the McKenzie method alone were analyzed, measuring short-term pain and disability through meta-analysis using random-effects models. The risk of bias of the included studies was assessed using the Cochrane Collaboration tool. &lt;b&gt;Results:&lt;/b&gt; Seven studies were included (&lt;i&gt;N&lt;/i&gt; = 441). The combination of therapeutic exercise with electrotherapy showed a significant reduction in pain (SMD -0.76 [-1.36, -0.16] (&lt;i&gt;p&lt;/i&gt; = 0.01; 95% CI)), without additional benefits for disability (SMD -0.94 [-2.08, 0.20] (&lt;i&gt;p&lt;/i&gt; = 0.1; 95% CI)) compared to exercise alone. Similarly, the McKenzie method presented statistically significant differences compared to other active interventions in reducing pain (SMD -0.61 [-1.01, -0.21] (&lt;i&gt;p&lt;/i&gt; = 0.003; 95% CI)), while no significant differences were found for disability (SMD -0.31 [-1.78, 1.15] (&lt;i&gt;p&lt;/i&gt; = 0.67; 95% CI)). Heterogeneity among studies was generally high. The results show short-term effects measured after completion of the intervention. &lt;b&gt;Conclusions:&lt;/b&gt; Electrotherapy combined with exercise may provide short-term relief of nonspecific chronic neck pain, although the certainty of evidence is very low. Interferential current plus exercise and isolated McKenzie exercises showed short-term pain improvements, with no consistent benefits for disability. The methodological limitations, heterogeneity, small samples, and short follow-up warrant cautious interpretation. High-quality trials with standardized protocols and longer follow-up are needed.</t>
-        </is>
-      </c>
+          <t>Efficacy of mobilization with movement in chronic shoulder pain: a systematic review and meta-analysis of controlled trials.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sánchez-Ferre Cristian, Lara-Palomo Inmaculada Carmen, González-Nula Ana Belén, Abad-Querol José, Gómez-García Silvia, Álvarez-López Elena, Matarán-Peñarrocha Guillermo Adolfo, Castro-Sánchez Adelaida María</t>
+          <t>Storås Arnstein, Lillebostad Fabian, Haslerud Sturla, Bjordal Jan Magnus, Leal-Junior Ernesto Cesar Pinto, Johnson Mark I, Stausholm Martin Bjørn</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Journal of clinical medicine</t>
+          <t>BMC musculoskeletal disorders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pubmed/41827107</t>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/41862863</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>41677133</t>
+          <t>41796312</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Exercise-Induced modulation of molecular-enriched functional connectivity in Parkinson's disease.</t>
+          <t>The effects of physiotherapy on neck pain with associated symptoms, ıncludıng cervicogenic dizziness and tinnitus: a systematic review.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Parkinson's disease (PD) involves degeneration of dopaminergic neurons and dysfunction across multiple neurotransmitter systems, contributing to both motor and cognitive impairments. Aerobic exercise improves clinical outcomes; however, its underlying neural mechanisms remain unclear. Using conventional resting-state fMRI combined with Receptor-Enriched Analysis of functional Connectivity by Targets (REACT), we examined molecular-enriched motor network changes following six months of supervised aerobic training in PD. Exercise-related connectivity changes were inversely correlated with baseline PD-healthy control differences, reflecting a partial normalization of PD-altered motor networks. Molecular-enriched analyses revealed selective effects on dopaminergic (FDOPA-enriched) and cholinergic (VAChT-enriched) related networks, with no changes observed in networks associated with serotonergic or noradrenergic systems. These findings provide supporting evidence for potential mechanistic links between aerobic exercise and network reorganization in PD, highlight multisystem effects, and illustrate the utility of molecular-enriched fMRI for probing neurotransmitter-specific interventions.</t>
+          <t>To systematically review the effectiveness of physiotherapy in people with neck pain and concurrent cervicogenic dizziness and/or tinnitus. Database searches were performed in PubMed, Embase, Web of Science, and PEDro (Physiotherapy Evidence Database). The primary outcome was pain-related factors and secondary outcomes were self-reported measures of dizziness-, tinnitus- and psychological-related factors, and objective functional status in the short(&lt; 3 months)-, intermediate(≥ 3 to &lt; 12 months), and long-term(≥ 12 months). The population of interest was people with neck pain and concurrent cervicogenic dizziness and/or tinnitus. The literature search was conducted in December 2022, with an update in June 2024. Risk of bias was assessed using the revised Cochrane Risk of Bias Tool for randomized controlled trials, and the strength of the conclusion was assessed using the evidence-based guideline development (EBRO) approach. A narrative approach was conducted to synthesize the data. Thirteen studies (&lt;i&gt;n&lt;/i&gt; = 785 patients) were analyzed, of which 10 were at high risk of bias, one raised some concers, and two were at low risk of bias. In the short-term, mulligan mobilization provided a higher improvement in CROM but showed no differences in balance with moderate evidence, and pain intensity and self-perceived handicap imposed by dizzines with conflicting evidence when compared to placebo treatment. Limited or no evidence was found for remaining pain-, dizziness, tinnitus- and psychological-related factors, and objective functional status after physiotherapy compared to wait-list or placebo treatment, and between different forms of physiotherapy. The analysis of the literature revealed that most studies (10 studies; 77%) have overall poor methodologic quality and are at high risk of bias. Findings suggest that mulligan mobilization is more beneficial for CROM, but has similar effects on balance in the short term compared to placebo treatment. Further research would be needed to establish firm conclusions for intermediate- and longer‐term efficacy of physiotherapy, as well as its effect on pain-, tinnitus- and psychological-related factors, and objective functional status. PROSPERO Registration Number: CRD42023394443. The online version contains supplementary material available at 10.1186/s12891-026-09664-6.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Reimers Erik, Bevington Connor, Hanania Jordan U, Dhaliwal Sahib, McKenzie Jess, Stein Ryan, Liu-Ambrose Teresa, Stoessl A Jon, Sossi Vesna</t>
+          <t>Canlı Kübra, De Greef Indra, Van Looveren Eveline, Meeus Mira, Cagnie Barbara, De Meulemeester Kayleigh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Journal of Parkinson's disease</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Humans, Parkinson Disease, Magnetic Resonance Imaging, Male, Middle Aged, Female, Aged, Exercise, Nerve Net, Exercise Therapy, Connectome, Brain</t>
-        </is>
-      </c>
+          <t>BMC musculoskeletal disorders</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pubmed/41677133</t>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/41796312</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>41660938</t>
+          <t>41245284</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>'Have a go, you might surprise yourself': a qualitative study of the experiences of autistic adolescents and young adults of a community gym-based exercise programme.</t>
+          <t>Comparing the Effectiveness of Mulligan Movement with Mobilization and Proprioceptive Neuromuscular Facilitation Techniques in Rehabilitation of Rotator Cuff Syndrome: A Randomized Controlled Trial.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>To explore the experiences of Autistic adolescents and young adults who participated in a 12-week student-mentored community based physical activity program called &lt;i&gt;FitSkills&lt;/i&gt;. This qualitative study was embedded within a large implementation trial. The data sources were: (i) trial screening forms, including reasons for participation from 30 Autistic young people (24 with intellectual disability), and (ii) semi-structured interviews completed by telephone with 7 Autistic young people (6 male; &lt;i&gt;M&lt;sub&gt;age&lt;/sub&gt;&lt;/i&gt; 18.6 years), 13 parents (11 mothers) and 16 student mentors (10 women). Data were analysed using content analysis (screening) and reflective thematic analysis (interviews). The most common reason Autistic young people and their parents gave for wanting to take part in &lt;i&gt;FitSkills&lt;/i&gt; was improving physical fitness. Three themes were identified: (1) Relationships with student mentors 'made it' and evolved over time to becoming gym partners or friends; (2) Social support helped participants to navigate the gym environment, manage sensory needs and establish a routine; and (3) Exercise was perceived to have a positive effect on psychological wellbeing. A student-mentored community-based program can facilitate Autistic young people to exercise, by overcoming barriers to their participation and supporting them to navigate the community gym environment.</t>
+          <t>This study aims to compare the effectiveness of Mulligan Movement with Mobilization Techniques (MWMs) and Proprioceptive Neuromuscular Facilitation Techniques (PNF) on pain intensity, range of motion (ROM), proprioception, scapular dyskinesis, functionality, and quality of life (QoL) in individuals with Rotator Cuff Syndrome (RCS). In this randomized, controlled, three-arm clinical trial, we recruited patients with Rotator Cuff Syndrome. During the study period, 70 patients diagnosed with Rotator Cuff Syndrome were screened and 60 eligible volunteers were enrolled. Patients were randomly allocated (1:1:1) into one of three groups: the control group (conservative treatment alone), the MWMs group (MWMs plus conservative treatment), and the PNF group (PNF plus conservative treatment). Each group underwent a total of 20 treatment sessions following prescribed programs, lasting 45 min per session and conducted five days a week. Pain intensity was evaluated using the Visual Analog Scale; joint ROM was measured with a Goniometer; proprioception was assessed using the Angle Reproduction Test; scapular dyskinesis was evaluated using the Lateral Scapular Slide Test; functionality was assessed with the Western Ontario Rotator Cuff Index; and QoL was evaluated using the Short Form-36. In the comparison between groups, MWMs had a significant effect on pain intensity, proprioception sense of 90° abduction movement and functionality (η2 (%95 CI): 0.393 (0.185; 0.531); 0.198 (0.033; 0.352); 0.429 (0.221; 0.561), respectively). It was observed that the control group was superior to other treatments in quality of life, except for the mental health sub-dimension (&lt;i&gt;p&lt;/i&gt; &lt; 0.05). The three interventions compared in patients with RCS have shown positive effects, with the MWMs found to be particularly superior in reducing pain, improving proprioception, and enhancing functionality, making it a valuable option for rehabilitation in clinical practice.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Shields Nora, Cleary Stacey L, McKenzie Georgia, Hawke Lyndon, Bury Simon, Taylor Nicholas F</t>
+          <t>Kirkaya Adem Can, Atici Emine, Aydin Gamze, Surenkok Ozgur</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Disability and rehabilitation</t>
+          <t>Indian journal of orthopaedics</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pubmed/41660938</t>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/41245284</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-06-16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>41648796</t>
+          <t>41102099</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chiropractic management of L5-S1 disc protrusion in an elite speed skater: a case report.</t>
+          <t>Consensus-based guidelines for intervention protocols targeting the foot spring mechanism during landing: A modified Delphi study.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>To describe clinical outcomes and return-to-play following multimodal chiropractic management of an elite speed skater with acute L5-S1 disc protrusion and S1 radiculopathy. A 20-year-old male elite speed skater presented with sudden-onset severe lumbosacral pain and S1 dermatomal symptoms during ice training. Assessment revealed positive straight leg raise at 40 degrees, diminished reflexes, and motor weakness consistent with S1 radiculopathy. Day 3 MRI confirmed mild L5-S1 disc protrusion with S1 nerve root impingement. McKenzie-based directional preference exercises with lumbar extension movements demonstrating centralization phenomenon. Treatment included progressive loading rehabilitation with sport-specific movement patterns through structured phases, McKenzie exercises performed 3-4 times daily (3-5 sets of 10-12 repetitions), and coordinated multidisciplinary care with physiotherapy, massage therapy, and strength coaching. Complete return to competitive speed skating within 4.8 months with sustained participation without symptom recurrence at 12-month follow-up. Notable 5-second personal best improvement in week 9 of rehabilitation. Conservative chiropractic management utilizing McKenzie-based protocols within a coordinated multidisciplinary framework achieved excellent outcomes in this elite athlete with lumbar disc herniation and radiculopathy, including successful return to competitive performance with enhanced outcomes.</t>
+          <t>To reach consensus of opinion on exercise selection and prescription guidelines for training the energetic function of the foot for landing tasks. A modified Delphi design with three rounds of questionnaires. Twenty-eight expert participants (clinicians n = 16, biomechanists n = 9, exercise physiologist n = 1, sport/exercise scientist n = 1, and athletic trainer n = 1) completed three rounds of questionnaires whereby they answered open-ended questions about optimal foot function, suggested exercises and prescription parameters to target the foot spring and ranked their level of agreement to exercises and prescription statements on 5-point Likert scales. Forty-six exercises were presented to participants, of which 23 reached consensus of agreement. Fifty-four exercise prescription statements were generated from the open responses of participants, and of these, 21 statements reached consensus of agreement, and one reached consensus of disagreement. The exercises that reached consensus were multi-joint, functionally integrated exercises. The exercises included plyometric-based exercises, which is consistent with published literature that has shown that plyometric training increases musculotendinous stiffness and energy recycling. The exercises, however, were dissimilar to exercises previously used in foot training literature. The exercise prescription statements that reached consensus aligned with American College of Sports Medicine (ACSM) exercise prescription guidelines, and the prescription parameters used in plyometric-training literature.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Chong Yeewon, Pollard Henry</t>
+          <t>Radcliffe Ceridwen R, Brown Nicholas A T, Newman Phil, Bull Jerushah J, Foot Spring Training Consensus Group, Spratford Wayne A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The Journal of the Canadian Chiropractic Association</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>Journal of science and medicine in sport</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Humans, Delphi Technique, Foot, Consensus, Biomechanical Phenomena, Plyometric Exercise, Surveys and Questionnaires</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pubmed/41648796</t>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/41102099</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-09-29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>41390815</t>
+          <t>41037047</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Human cerebrospinal fluid net flow enhanced by respiration during the awake state.</t>
+          <t>Immediate Effects of Manual Therapy Techniques on Ankle Dorsiflexion: A Randomized Clinical Trial.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cerebrospinal fluid dynamics play a crucial role in maintaining brain homeostasis by delivering nutrients, transmitting immune signals, and clearing waste products. While cardiac activity primarily drives the pulsatile movement of cerebrospinal fluid, respiration has been shown to facilitate low-frequency oscillations and contribute to bulk flow. Recent studies suggest that enhancing respiratory function may be an effective intervention to modulate cerebrospinal fluid dynamics. This study included 20 individuals with long-term formal training in Seokmun Hoheup, a lower belly-centered breathing practice (mean ± SD age, 58.1 ± 17.3 years; 8 females), and 25 controls with no formal long-term breathing practice (mean ± SD age, 49.2 ± 20.2 years; 12 females). All underwent real-time velocity-encoding magnetic resonance imaging to assess cerebrospinal fluid movement at the foramen magnum and lateral ventricle during both regular breathing and deep breathing. Deep breathing enhances cerebrospinal fluid dynamics in both groups, increasing displacement and net flow, particularly at the foramen magnum. Seokmun Hoheup trained participants show greater cerebrospinal fluid movement than controls at both the foramen magnum and lateral ventricle. Even during regular breathing, trained participants show higher cerebrospinal fluid mean speed, displacement, and net flow. Among respiratory factors, inhale length and diaphragm displacement show the strongest correlations with cerebrospinal fluid movement. Respiration modulated cerebrospinal fluid dynamics through both mechanical enhancement of venous outflow and autonomic modulation of the heart, with mechanical effects predominating in the lateral ventricle and both pathways contributing to the foramen magnum. Our findings identify respiration in the awake state as a modifiable, noninvasive mechanism that influences involuntary functions such as cerebrospinal fluid dynamics and may have implications for cerebrospinal fluid-mediated brain homeostasis.</t>
+          <t>The purpose of this study was to evaluate the effects of combined techniques on ROM, performance, and dynamic postural balance in young adults. Sixty participants were recruited, with a mean age of 25.35 (±8.00) years and ankle dorsiflexion ROM below 40° in closed kinetic chain (CKC). The participants were randomly divided into 2 groups: Joint mobilization based on the Mulligan Concept (Group 1); Joint mobilization based on the Mulligan Concept, together with the Maitland Method (Group 2). The participants were evaluated preintervention (A0), immediately after the intervention (A1), and 3 to 4 days after the intervention (A2). DF ROM in CKC. ROM in open kinetic chain, performance, and balance. Group 2 presented superior performance in the Triple Hop Test in evaluations A1 (Cohen's d = 1.45) and A2 (Cohen's d = 1.21), and after the intervention (A2) showed greater displacement (Cohen's d = 3.22) in the Y Balance Test. Both groups showed increases of DF ROM in CKC and performance. The combination of joint mobilization techniques can provide additional benefits in functional performance. Both techniques are effective for increasing ankle DF ROM.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lim Seokbeen, Cogswell Petrice M, Jacobson David N, Kandimalla Mahathi, Choi Yurim, Nycklemoe Marin, Kim Daniel C, Karki Pragalv, Rossman Phillip J, McKenzie Zona, Park John G, Lee Sangwon, Ganji Sandeep, Kremers Walter K, Mark Ian T, Kang Daehun, In Myung-Ho, Gunter Jeffrey, Graff-Radford Jonathan, Benarroch Eduardo E, Huston John, Jack Clifford R, Petersen Ronald C, Lapid Maria I, Lowe Val J, Jung Daehyun, Min Paul H</t>
+          <t>Silva Matheus de Castro, Ferreira Arthur de Sá, Baldon Rodrigo de Marche, Lins Carolina, de Andrade Gustavo Martins, Pereira Gustavo Barros Braga de Castro, Silva Natalia Camin, Felício Lilian Ramiro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nature communications</t>
+          <t>Journal of manipulative and physiological therapeutics</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Humans, Female, Cerebrospinal Fluid, Male, Middle Aged, Magnetic Resonance Imaging, Respiration, Adult, Wakefulness, Aged, Breathing Exercises</t>
+          <t>Humans, Male, Female, Ankle Joint, Adult, Range of Motion, Articular, Musculoskeletal Manipulations, Postural Balance, Young Adult, Treatment Outcome</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pubmed/41390815</t>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/41037047</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-10-02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>41316625</t>
+          <t>40764267</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Comparison of the effectiveness of home-based video-supported McKenzie versus Pilates exercise programs in patients with chronic non-specific low back pain: a randomized controlled trial.</t>
+          <t>A comparison of two mobilization approaches on the acromiohumeral distance in overhead athletes with primary subacromial impingement syndrome: a randomized clinical study.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chronic non-specific low back pain (NSLBP) is a prevalent condition with significant socio-economic implications. The McKenzie and Pilates exercise methods are widely used physiotherapy interventions; however, comparative studies evaluating their effectiveness, particularly in home-based, video-supported formats, remain limited. This randomized controlled trial compared the short-term effects of video-supported McKenzie and Pilates exercises on pain, disability, pressure pain threshold, and lumbar mobility in adults with chronic NSLBP. Thirty-two participants with chronic NSLBP were randomly assigned to either a McKenzie (n = 16) or a Pilates (n = 16) exercise group. Both interventions were performed at home using instructional videos for three weeks. Outcome measures were assessed pre- and post-intervention and included the Visual Analog Scale (VAS) for pain intensity, the Roland-Morris Disability Questionnaire (RMDQ) for functional disability, pressure pain threshold (PPT) measured with algometry, and lumbar flexibility assessed with the Fingertip-to-Floor (FTF) test. The McKenzie group performed daily sessions (7 times/week), while the Pilates group exercised three times per week. Pain intensity (VAS) decreased by 28.0 mm in the McKenzie group and 25.6 mm in the Pilates group, with 62.5 % and 56.3 % of participants exceeding the MCID of 20 mm. Disability (RMDQ) improved by 3.4 and 2.8 points, respectively, but neither group surpassed the 3.5-point MCID. Pressure pain threshold increased bilaterally (right: +13.2 vs. +11.7 N/cm&lt;sup&gt;2&lt;/sup&gt;; left: +9.9 vs. +6.6 N/cm&lt;sup&gt;2&lt;/sup&gt;), exceeding the MDC (6-9 N/cm&lt;sup&gt;2&lt;/sup&gt;) in most cases. Lumbar flexibility (FTF) improved by 5.3 cm and 6.8 cm, respectively, with 56.3 % and 75.0 % exceeding the MDC. No significant between-group differences or adverse events were observed. Both interventions improved outcomes over 3 weeks in individuals with chronic NSLBP. Larger trials with longer follow-up are warranted to confirm these results and guide implementation.</t>
+          <t>Shoulder mobilization techniques, with and without movement, may restore the range of intra-articular glenohumeral motions and expand the subacromial space during arm abduction. The primary purpose of this study was to measure and compare the acromiohumeral distance at three static angles of passive scapular arm abduction (no arm abduction, 45° of arm abduction, and 60° of arm abduction) in overhead athletes diagnosed with primary subacromial impingement syndrome, before and after shoulder mobilization techniques with and without movement, combined with contemporary physical therapy. Fifty-one overhead athletes diagnosed with primary subacromial impingement syndrome were randomly assigned to three parallel groups. One intervention group received the Mulligan shoulder mobilization techniques, whereas the other intervention group received the Maitland shoulder mobilization techniques. Both mobilization approaches were accompanied by contemporary physical therapy and were administered every other day for two weeks. The control group received no specific intervention for two weeks. Using an ultrasound device, the acromiohumeral distance was assessed in the intervention groups one day before and one day after treatment with manual therapy and in the control group at two-week intervals. Both the Mulligan and Maitland approaches significantly increased the acromiohumeral distance at all three static angles of passive scapular arm abduction (p-values &lt; 0.001). In contrast, no significant changes were observed in the control group (p-values &gt; 0.317).The Mulligan approach, compared to the Maitland approach, exhibited significantly greater increases in the acromiohumeral distance at all three static angles of passive scapular arm abduction (p-values &lt; 0.001). Both the Mulligan and Maitland shoulder mobilization techniques, combined with contemporary physical therapy, significantly increased the acromiohumeral distance at static angles of passive scapular arm abduction in individuals suffering from primary subacromial impingement syndrome. Moreover, the Mulligan approach provided significantly greater improvements in the acromiohumeral distance compared to the Maitland approach.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zygouna Lamprini, Lytras Dimitrios, Kasimis Konstantinos, Chatziprodromidou Ioanna P, Apostolou Thomas, Iakovidis Paris</t>
+          <t>Khandaloo Ali, Taghizadeh Delkhoush Cyrus, Paknazar Fatemeh, Ehsani Fatemeh, Shokrian Zohreh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Journal of bodywork and movement therapies</t>
+          <t>The Journal of manual &amp; manipulative therapy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Humans, Low Back Pain, Female, Male, Middle Aged, Exercise Movement Techniques, Adult, Pain Measurement, Pain Threshold, Chronic Pain, Disability Evaluation, Exercise Therapy, Range of Motion, Articular, Treatment Outcome</t>
+          <t>Humans, Shoulder Impingement Syndrome, Male, Female, Adult, Range of Motion, Articular, Acromion, Young Adult, Musculoskeletal Manipulations, Humerus, Treatment Outcome, Physical Therapy Modalities, Athletes, Athletic Injuries</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pubmed/41316625</t>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/40764267</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-08-05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41180947</t>
+          <t>40747193</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ansa Cervicalis to Marginal Mandibular Nerve Transfer, a Feasible Option to Improve Lower Lip Function in Facial Nerve Paralysis.</t>
+          <t>Combining the Effects of Mobilization With Movement and Cyriax Physiotherapy in Lateral Epicondylitis: A Case Report.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Facial nerve palsy affecting the lower face may compromise essential functions such as speech and eating. The associated facial asymmetry can contribute to social isolation. Facial nerve reconstruction using a combination of interposition nerve grafts and/or nerve transfers offers significant improvement. However, these options are limited by insufficient donor nerves and unwanted synkinesis if a single donor nerve is used for the entire hemi-face. To ameliorate both limitations, we perform an ansa cervicalis to marginal mandibular nerve transfer to restore tone and symmetry to the lower third of the face. We have found this a safe and feasible technique with minimal donor site morbidity. The anatomy is favorable both in terms of donor nerve length and size match between nerves. We report 9 cases with at least 6 months follow up which demonstrate improved lower lip tone and symmetry and improved oral competence. Early donor site morbidity and postoperative complications are minimal. This method is a reliable adjunct in facial nerve reconstruction to address the marginal mandibular nerve paralysis.</t>
+          <t>Tennis elbow, or lateral epicondylitis (LE), is characterized by a gradual onset of pain over the lateral aspect of the elbow, particularly during wrist extension with a pronated or supinated hand. It is often exacerbated by gripping activities. Common symptoms include pain at the origin of wrist extensor tendons, reduced grip strength, and impaired upper limb function. The etiology may include trauma, degeneration, repetitive grasping, scar tissue formation, or contractures. Diagnosis is based on patient history, functional tests, and palpation of the lateral epicondyle. A 48-year-old woman, a homemaker complained of right elbow pain and swelling and was diagnosed with LE. Pain intensity was assessed with a Visual Analogue Scale (VAS) and functional ability with Patient-Rated Tennis Elbow Evaluation (PRTEE). This case report aims to evaluate the combined effect of mobilization with movement (MWM) and Cyriax physiotherapy on pain reduction and functional improvement in a patient with LE over a two-week intervention period. As a result of physical therapy sessions, pain levels decreased substantially, from 8/10 to 2/10 on the VAS, and improvement in functional ability went from 81/100 to 34/100 in PRTEE. This case suggests that combining MWM and Cyriax physiotherapy techniques may enhance pain relief and functional improvements in patients with LE. Further research with larger statistically significant samples is needed to confirm these findings.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Van der Vyver Marieta, Lindell-Jonsson Eva, Bell Kristin N L, Singh Ashvir, Chandarana Shamir P, Harrop Alan Robertson, Hart Robert D, Matthews Wayne T, Hinther Ashley, McKenzie Charles David, Matthews Jennifer K L, Schrag Christiaan</t>
+          <t>S Sivakumar, Reddy C Ravindra, Jayabalan Prakash</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Plastic surgery (Oakville, Ont.)</t>
+          <t>Cureus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pubmed/41180947</t>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/40747193</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41095489</t>
+          <t>40724787</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Comparison of Kaltenborn-Evjenth, McKenzie, and HVLA Manipulation Techniques in the Treatment of Lumbar Spine Pain: A Review of the Literature.</t>
+          <t>The Effectiveness of Manual Therapy in the Cervical Spine and Diaphragm, in Combination with Breathing Re-Education Exercises, on the Range of Motion and Forward Head Posture in Patients with Non-Specific Chronic Neck Pain: A Randomized Controlled Trial.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lumbar spine pain (LBP) is a leading cause of disability worldwide and remains a major challenge in clinical practice. Among non-invasive treatment strategies, manual therapy plays a central role, offering individualized interventions that target both biomechanical dysfunction and pain. This narrative review compares three commonly used physiotherapeutic approaches-Kaltenborn-Evjenth mobilization, the McKenzie method, and high-velocity low-amplitude (HVLA) manipulation-based on current evidence regarding their effectiveness, safety, and clinical application. A total of 32 randomized controlled trials, systematic reviews, and meta-analyses published between 2003 and 2024 were analyzed. The Kaltenborn-Evjenth method demonstrated notable effectiveness in improving range of motion and reducing chronic pain, particularly in patients with segmental hypomobility. The McKenzie method showed strong outcomes in both acute and chronic LBP, especially in cases involving symptom centralization and high patient engagement. HVLA techniques offered rapid symptom relief in acute phases but required careful patient selection due to their mechanical intensity. The findings suggest that no single method is universally superior. Instead, optimal outcomes are achieved through individualized treatment plans that integrate multiple techniques based on clinical presentation, pain chronicity, and functional limitations. Multimodal strategies that combine manual therapy with exercise and patient education appear to be the most effective in managing LBP and preventing recurrence.</t>
+          <t>&lt;b&gt;Background/Objectives:&lt;/b&gt; A randomized controlled trial (RCT) was designed to test the emerging role of respiratory mechanics as part of physiotherapy in patients with non-specific chronic neck pain (NSCNP). &lt;b&gt;Methods:&lt;/b&gt; Ninety patients with NSCNP and symptom duration &gt;3 months were randomly allocated to three intervention groups of equal size, receiving either cervical spine (according to the Mulligan Concept) and diaphragm manual therapy plus breathing reeducation exercises (experimental group-EG1), cervical spine manual therapy plus sham diaphragmatic manual techniques (EG2), or conventional physiotherapy (control group-CG). The treatment period lasted one month (10 sessions) for all groups. The effect on the cervical spine range of motion (CS-ROM) and on the craniovertebral angle (CVA) was examined. Outcomes were collected before treatment (0/12), after treatment (1/12), and three months after the end of treatment (4/12). The main analysis comprised a two-way mixed ANOVA with a repeated measures factor (time) and a between-groups factor (group). Post hoc tests assessed the source of significant interactions detected. The significance level was set at &lt;i&gt;p&lt;/i&gt; = 0.05. &lt;b&gt;Results:&lt;/b&gt; No significant between-group baseline differences were identified. Increases in CS-ROM and in CVA were registered mainly post-treatment, with improvements maintained at follow-up for CS-ROM. EG1 significantly improved over CG in all movement directions except for flexion and over EG2 for extension only, at 1/12 and 4/12. All groups improved by the same amount for CVA. &lt;b&gt;Conclusions:&lt;/b&gt; EG1, which included diaphragm manual therapy and breathing re-education exercises, registered the largest overall improvement over CG (except for flexion and CVA), and for extension over EG2. The interaction between respiratory mechanics and neck mobility may provide new therapeutic and assessment insights of patients with NSCNP.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Grzegorczyk Michał, Brodowicz-Król Magdalena, Brzuszkiewicz-Kuźmicka Grażyna</t>
+          <t>Tatsios Petros I, Grammatopoulou Eirini, Dimitriadis Zacharias, Koumantakis George A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -803,54 +799,1658 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pubmed/41095489</t>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/40724787</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-07-21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>40990623</t>
+          <t>40523400</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A pilot randomised controlled trial of an online self-management programme for people with persistent pain post-knee replacement (Kneed).</t>
+          <t>Comparison of effectiveness of Mulligan mobilization technique and cervical stabilization training in patients with chronic neck pain: a single-blinded randomized controlled trial.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ObjectiveModerate to severe persistent pain can affect up to 25% of people after a knee replacement for osteoarthritis. The aim of the trial was to test the feasibility of implementing Kneed, a novel digital pain rehabilitation self-management programme.DesignProspective, two group parallel randomised pilot study.SettingOnline in Australia.ParticipantsAdults with persistent pain rated as ≥4/10 in the operated knee more than 3 months post-knee replacement for osteoarthritis.InterventionThe Kneed group were provided with 8 weeks of access to a digital pain rehabilitation self-management programme and compared to usual care.Main measuresRecruitment, acceptability, usability and limited efficacy with descriptive statistics.ResultsSixty participants, mean age 68.7 years, 75% female, 66.7% retired and 43% living outside metropolitan areas, were recruited between 15 October and 19 December, 2024 via social media advertising with 418 online eligibility surveys performed. There were 190 (45.5%) deemed potentially eligible; 82 (19.6%) left contact details and 60 (14.4%) consented. At 8 weeks, there were 48 (80%) participants remaining in the trial (20 Kneed (64.5%), 28 usual care (96.6%)). A majority of the Kneed group found the Kneed programme acceptable, would use it again and found that it helped them effectively manage pain and function.ConclusionIt is feasible to recruit and retain older Australians with moderate to severe knee pain post-knee replacement for a trial testing a digital pain rehabilitation self-management programme. A larger trial is indicated to further test the clinical effectiveness of Kneed to reduce pain and improve function.</t>
+          <t>The purpose of the current study was to compare the effectiveness of Mulligan mobilization technique (MMT) and cervical stabilization training (CST) in patients with chronic neck pain.Thirty-six patients with chronic neck pain were randomly assigned to three groups as control, MMT, and CST groups. In the current study, pain intensity, range of motion (ROM), proprioception, head posture, deep neck flexor (DNF) muscle endurance, disability level, and neck awareness were evaluated as outcome measures.All variables showed statistically significant changes following treatment in all groups. MMT and CST were found to be more effective than home exercise regimen (control group) in pain intensity (p=0.001), DNF muscle endurance (p=0.0001), and disability level (p=0.007) but they were not superior to each other. MMT was found to be more effective in increasing ROM (p=0.0001) and neck awareness (p=0.018). Also, CST was found to be more effective in improving head posture (p=0.0001) and proprioception (p=0.001).The study indicated MMT was more effective in increasing ROM and neck awareness, and the CST was more effective in improving head posture and proprioception. Comprehensive perspective can be acquired for health professionals in this field to select the appropriate rehabilitation approaches for patients with chronic neck pain thanks to our results.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Johns Nathan, McKenzie Dean, Brady Bernadette, Naylor Justine, Olver John</t>
+          <t>Sekeroz Serbay, Telci Emine Aslan, Buke Meryem, Akkaya Nuray</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Clinical rehabilitation</t>
+          <t>Die Rehabilitation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Humans, Female, Pilot Projects, Aged, Male, Self-Management, Arthroplasty, Replacement, Knee, Osteoarthritis, Knee, Middle Aged, Australia, Pain Management, Feasibility Studies, Pain Measurement, Postoperative Pain, Treatment Outcome</t>
+          <t>Humans, Neck Pain, Female, Male, Treatment Outcome, Middle Aged, Adult, Chronic Pain, Range of Motion, Articular, Exercise Therapy, Single-Blind Method, Musculoskeletal Manipulations, Pain Measurement</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pubmed/40990623</t>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/40523400</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>40498063</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Effect of Mulligan manual therapy and exercise on headache frequency, intensity, disability, and upper cervical joint hypomobility in people with episodic tension-type headache: a randomized clinical trial.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The effectiveness of Mulligan manual therapy has been investigated in cervicogenic headache but not in tension-type headache (TTH). To compare the effectiveness of exercise + Mulligan manual therapy over exercise or exercise + sham in episodic TTH. Using a randomized clinical trial design, 99 subjects with episodic TTH received six sessions of allocated intervention over 4 weeks. Headache frequency, intensity, duration, medication intake, disability, upper cervical rotation, pressure-pain thresholds, and patient satisfaction were assessed at baseline, 4 weeks, 3, and 6 months. Headache frequency reduced significantly in group exercise + Mulligan manual therapy compared to group exercise post-intervention (MD -1.0 day, 95% CI -2.0 to -0.0) (&lt;i&gt;p&lt;/i&gt; = .002), and at 3-month follow-up (MD -1 days, 95% CI -2.0 to 0.0) (&lt;i&gt;p&lt;/i&gt; = .002), but only at post-intervention compared to group exercise + sham (MD 1.0 day, 95% CI 0.0 to 2.0) (&lt;i&gt;p&lt;/i&gt; = .008). The clinical relevance is unclear as between-group differences did not reach a clinical threshold. No difference was observed at 6 months (&lt;i&gt;p&lt;/i&gt; &gt; .17). A similar trend was observed for other outcomes. There was no difference between groups exercise and exercise + sham for any outcome (&lt;i&gt;p&lt;/i&gt; &gt; .17). In episodic TTH, exercise + Mulligan manual therapy provided short-term clinically uncertain improvements in headache parameters. These results differ to studies of cervicogenic headache. Unsuitability of Mulligan manual therapy for underlying pathophysiological mechanisms in episodic TTH may explain these results. Practitioners should consider Mulligan manual therapy for selected patients and only as part of evidence-based multimodal management of episodic TTH. CTRI/2019/06/019506.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Satpute Kiran, Bedekar Nilima, Hall Toby</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Physiotherapy theory and practice</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Humans, Female, Male, Tension-Type Headache, Adult, Exercise Therapy, Musculoskeletal Manipulations, Middle Aged, Treatment Outcome, Pain Measurement, Disability Evaluation, Cervical Vertebrae, Time Factors, Young Adult</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/40498063</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>40439260</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Effectiveness of Mulligan's Techniques in Non-Specific Neck Pain: A Systematic Review and Meta-Analysis.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mulligan's techniques, such as Sustained Natural Apophyseal Glides (SNAGs) and Natural Apophyseal Glides (NAGs), are commonly applied by physiotherapists when treating patients with non-specific neck pain (NP). However, there has been no comprehensive synthesis of their effects in NP. This review aimed to assess the effectiveness of Mulligan's techniques in reducing pain, improving disability, and enhancing cervical range of motion (CROM) in adults with acute, subacute, or chronic NP. A systematic review with meta-analysis was conducted on randomized controlled trials (RCTs) comparing Mulligan's techniques with other interventions in adults with NP. Two reviewers independently conducted study selection, data extraction, and risk of bias (RoB) assessment. Meta-analyses were performed when clinical homogeneity was present; otherwise, a narrative synthesis was used. Certainty of evidence was rated using the Grading of Recommendations, Assessment, Development and Evaluations (GRADE) approach. Thirty-three studies were included. For acute and mixed (acute/subacute/chronic) NP, Mulligan's techniques were no more effective than other interventions for pain reduction, disability improvement, or CROM enhancement. However, in patients with chronic or uncertain chronicity NP, SNAGs combined with other interventions demonstrated superior outcomes-both statistically and sometimes clinically-compared to certain treatments like exercises and muscle-energy techniques, for reducing pain and disability and improving CROM. The certainty of evidence was rated very low. Mulligan's techniques appear to be safe, simple, and potentially beneficial for managing mixed or chronic NP when combined with other interventions, presenting results that may be comparable or occasionally superior to other standard techniques. Physiotherapists may consider incorporating Mulligan's techniques, especially SNAGs, within broader NP treatment strategies, as they offer a feasible, low-risk option for improving patient outcomes, particularly for chronic NP cases when used alongside other therapies.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Barbosa-Silva Jordana, Luc Alexandre, Sobral de Oliveira-Souza Ana Izabela, Martins de Abreu Raphael, Cipriano Jakelline, de Schaetzen Marine, Pitance Laurent, Armijo-Olivo Susan</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Physiotherapy research international : the journal for researchers and clinicians in physical therapy</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Humans, Neck Pain, Physical Therapy Modalities, Range of Motion, Articular, Randomized Controlled Trials as Topic, Treatment Outcome</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/40439260</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2025-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>40301893</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The effectiveness of mulligan mobilization with movement (MWM) on outcomes of patients with ankle sprain: a systematic review and meta-analysis.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ankle sprains are common injuries that cause pain, swelling, and reduced range of motion (ROM), adversely affecting physical activity. In this study, we aim to review the effectiveness of mobilization with movement (MWM) in improving outcomes for patients with ankle sprains. We conducted a search of PubMed, Cochrane Library, PEDro, Web of Science, and Scopus up to October 2023 for English trials comparing Mulligan MWM with other treatments. The Cochrane Risk of Bias tool (ROB 2) was used for quality assessment, and mean differences (MD) with 95% confidence intervals (CI) were calculated. Heterogeneity was evaluated using Cochrane's Q and I&lt;sup&gt;2&lt;/sup&gt; statistics. A total of 10 trials involving 419 patients (209 in the MWM group and 210 controls) were included. The overall risk of bias was low. MWM significantly reduced pain (MD = - 0.92; 95% CI:[- 1.37, - 0.46]; P &lt; 0.0001) and improved ankle ROM (SMD = 1.65; 95% CI:[0.17, 3.14]; P = 0.03). MWM also demonstrated superior performance in the Star Excursion Balance Test (SEBT) (MD = 3.15; 95% CI:[1.44, 4.86]; P = 0.0003) and Y Balance Test (MD = 4.69; 95% CI:[1.67, 7.70]; P = 0.02). However, no significant differences were found in pain pressure threshold (SMD = - 0.10; 95% CI:[- 0.59, 0.39]; P = 0.7), stiffness perception (MD = 0.10; 95% CI:[- 0.64, 0.85]; P = 0.79), or peroneus longus latency time (MD = - 12.85; 95% CI:[- 22.08, - 3.63]; P = 0.006). The quality evaluation showed that the majority of RCTs revealed some concerns, except of two studies that established a low risk of bias. The GRADE assessment classified the overall evidence as low or very low, due to imprecision, risk of bias, and inconsistency. MWM significantly reduced pain and improved ROM and WBLT scores in patients with ankle sprains. The MWM group also showed enhanced balance in the posterolateral SEBT compared to controls.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ElMeligie Mohamed M, Abdeen Heba A, Atef Hady, Marques-Sule Elena, Karkosha Rania N</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BMC sports science, medicine &amp; rehabilitation</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/40301893</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>40265821</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mobilization with movement on reducing pain and disability for knee osteoarthritis: a systematic review and meta-analysis of randomized controlled trials.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Knee osteoarthritis (OA), affecting both tibiofemoral and patellofemoral compartments, causes pain and reduced quality of life. The Mulligan Concept of mobilization with movement (MWM) may relieve symptoms by modifying sensory input, enhancing central inhibition, and improving motor activation. This study conducted a systematic review and meta-analysis with subgroup analysis to evaluate MWM's efficacy in improving pain and disability in knee OA. Electronic databases were searched from inception to January 2025 for randomized controlled trials (RCTs) on the effects of MWM on knee OA. Pain intensity and disability improvement, standardized using Hedges' g, were the primary and secondary outcomes. Two reviewers independently assessed study quality, extracted data, and performed a meta-analysis using a random-effects model. Subgroup analyses considered intervention regimens, technique including weight-bearing or not, Kellgren-Lawrence (K-L) classification grades, and control group comparisons. From 2&lt;i&gt;3&lt;/i&gt; RCTs (&lt;i&gt;996&lt;/i&gt; participants; mean age 37-61 years), MWM significantly reduced pain (Hedges' g = -0.984, 95% CI = -1.375 to -0.593) and improved disability (Hedges' g = -1.041, 95% CI = -1.477 to - 0.606).. Greater effect sizes were observed when MWM was combined with other therapies, including weight-bearing positions, and among participants without advanced K-L grades. MWM also demonstrated significant effects in comparison with active controls. This meta-analysis showed that MWM reduces pain and disability in individuals with knee osteoarthritis, especially when incorporated into treatment protocols featuring weight-bearing positions and combined physical therapies. Clinically, MWM could be incorporated into rehabilitation programs to enhance pain relief and functional recovery. Future studies should extend follow-ups and address bias.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lin Long-Huei, Lin Min, Hsieh Guo-Jia, Chen Hsin-I, Sun Shu-Fen, Tsai Ren Jei</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The Journal of manual &amp; manipulative therapy</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Humans, Osteoarthritis, Knee, Randomized Controlled Trials as Topic, Pain Management, Musculoskeletal Manipulations, Middle Aged, Pain Measurement</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/40265821</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>40190952</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The Short-Term Efficacy of Mulligan Traction Straight Leg Raise on Low Back Pain Associated With Hamstring Tightness in Young Adults.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Background and objective Low back pain (LBP) is a very common problem faced by people globally; with a prevalence rate of almost 84%, it is nowadays commonly seen in the young adult population too. This population is also prone to a sedentary lifestyle, leading to hamstring tightness. As this population has very little time to spare in terms of long-term treatment, the Mulligan traction straight leg raise (TSLR) technique might be ideal for them as it is effective even in a short amount of time and may help treat LBP and hamstring tightness in a noninvasive manner and improve flexibility simultaneously. Materials and methods For LBP, an assessment of the pain rating scale was performed. For hamstring tightness, the active knee extension test (AKET), V-sit and reach test, and fingertip-to-floor test were employed with the help of a goniometer, plinth, inch tape, and chalk. Mulligan TSLR was performed for three consecutive days. After three days, an assessment was conducted to record the level of improvement. Results The investigations were performed in 100 young adults of which 60 (60%) were females and 40 (40%) were males. Normal BMI was observed in 67 (67%) participants while the remaining 33 (33%) participants were in the overweight category. LBP and hamstring tightness decreased after the application of the treatment, and the difference with the pre-treatment situation was statistically significant(p&lt;0.0001). This signifies that the treatment is effective. Conclusions The present study demonstrated a significant reduction in LBP associated with hamstring tightness after the short-term application of Mulligan TSLR. Our findings show that this method alone can alleviate acute pain and tightness, leading to improvement in range of motion and muscle flexibility.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mane Aarya S, Yadav Trupti</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/40190952</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>40156270</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Mechanical correction in kinesiology and mulligan taping: A comparative study on scapular dyskinesis in computer users.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BackgroundPoor scapular resting position and abnormal motion with the lack of proper muscle performance contribute to the development of shoulder dysfunction and pain. Various taping methods was proven to stabilize the scapula in a retracted position and facilitate proper scapular motion.ObjectivesTo compare the effects of mechanical correction of kinesiology tape (KT) and mulligan tape (MuT) methods on electromyographic activity (EMG) and kinematics of scapulothoracic (ST) and kinetics of glenohumeral (GH) joints in computer users affected with scapular dyskinesis (SD).MethodsThis study is a single-blinded randomized placebo-controlled clinical trial study with convenience sampling. Thirty-six male computer users with SD were randomized in three groups of KT, MuT, and placebo tape (PT). A two-session evaluation, in each session two times, with a 72-h interval was done. The outcome measures of the EMG were peak root mean square (PRMS) and RMS activity of upper trapezius (UT), middle trapezius (MT), lower trapezius (LT), deltoid (Del), and serratus anterior (SA) muscles during typing and 120° of scaption tasks. Anterior tipping, upward rotation, and internal rotation of the scapula were also recorded using a motion capture system and processed using custom code written in Matlab (R2015b; Mathworks, Inc., Natick, MA).ResultsIn MuT, PRMS and RMS of UT and MT; PRMS of SA in 120° scaption; and RMS of MT in typing position increased significantly (p &lt; 0.05). In KT, SA RMS in 120° scaption increased and internal and upward rotation of scapula in typing position decreased significantly (p &lt; 0.05).ConclusionMulligan tape showed a better effect on increasing EMG activity of the muscles which have a controlling role in SD correction and KT had a better impact on decreasing scapula internal rotation which is typically impaired in SD.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Khaki Shahab, Ravanbod Roya, Ashtiani Mohammed N</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Journal of back and musculoskeletal rehabilitation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Humans, Male, Scapula, Athletic Tape, Adult, Electromyography, Single-Blind Method, Dyskinesias, Range of Motion, Articular, Biomechanical Phenomena, Shoulder Joint, Young Adult, Superficial Back Muscles</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/40156270</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>40102149</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The effect of Mulligan and Maitland techniques on pain, functionality, proprioception, and quality of life in individuals with rotator cuff lesions.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Rotator cuff disease treatment typically involves manual therapy and exercise as part of physical therapy. This study aims to investigate the effects of Mulligan and Maitland mobilization methods on pain, functionality, quality of life, and proprioception in individuals with rotator cuff lesions. STUDY DESIGN: This was a single-blinded randomized clinical trial. The study included 45 individuals with rotator cuff lesions. Participants were randomly divided into three groups: conventional exercise, Maitland mobilization, and Mulligan mobilization. All participants were assessed pretreatment and post treatment using the Visual Analog Scale, Disabilities of the Arm, Shoulder, and Hand, Rotator Cuff Quality of Life, range of motion (ROM), and proprioception. All parameters, except proprioception, improved significantly in all three groups post treatment (p &lt; 0.05). Mulligan group (MG) and Maitland mobilization group (MMG) had higher improvements to the conventional exercise group (CG) in terms of flexion ROM (p = 0.05, effect size = 0.22), abduction ROM (p = 0.02, effect size = 0.26), Disabilities of the Arm, Shoulder, and Hand (p &lt; 0.001, effect size = 0.56). Also, the MG group had greater improvements to the MMG and CG groups in terms of Rotator Cuff Quality of Life/symptoms (p &lt; 0.001, effect size = 0.43), job (p &lt; 0.001, effect size = 0.61), lifestyle (p &lt; 0.001, effect size = 0.42), emotional parameters (p &lt; 0.001, effect size = 0.29). MG was more effective than the MMG in Visual Analog Scale activity (p &lt; 0.001, effect size = 0.32), external rotation (p = 0.012, effect size = 0.19), and abduction ROM (p = 0.002, effect size = 0.26). However, no improvement in proprioception was observed across all groups (p &gt; 0.05). This study concluded that, in addition to conventional treatment, both Mulligan and Maitland mobilization therapy effectively improve range of motion, functionality, and quality of life.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Celik Tarik, Menek Burak</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Journal of hand therapy : official journal of the American Society of Hand Therapists</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Humans, Male, Female, Quality of Life, Proprioception, Middle Aged, Single-Blind Method, Range of Motion, Articular, Rotator Cuff Injuries, Pain Measurement, Adult, Exercise Therapy, Musculoskeletal Manipulations, Aged, Treatment Outcome, Disability Evaluation</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/40102149</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>40050244</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Immediate Effects of Mobilization With Movement Technique on Cervical Muscle Stiffness, Pain, and Range of Motion in Individuals With Mechanical Neck Pain: A Double-Blind Randomized Controlled Trial.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mulligan sustained natural apophyseal glide (SNAG) is a mobilization technique that aims to reduce pain and improve function by correcting positional errors in the facet joint. To investigate the immediate effects of the Mulligan SNAG application on muscle stiffness, pain, pressure pain threshold (PPT) and range of motion (RoM) in patients with chronic mechanical neck pain. A randomized, double-blind trial was conducted. Forty individuals with chronic mechanical neck pain (mean age = 39.35 ± 6.68 years) were randomized into two groups: Mobilization with movement group (MWMG), and sham group (SG). Muscle stiffness was measured with MyotonPro, pain intensity with Numerical Pain Rating Scale, cervical RoM with a digital inclinometer, and PPT with an algometer. Measurements were performed pre-and 5 minutes post-intervention in a single session. Muscle stiffness significantly changed in the MWMG for the left trapezius and right cervical extensors (&lt;i&gt;p&lt;/i&gt; = .003, effect size (ES) = 0.42; &lt;i&gt;p&lt;/i&gt; = .031, ES = 0.49, respectively), whereas no significant changes were observed in the SG (&lt;i&gt;p&lt;/i&gt; = .097, ES = 0.12; &lt;i&gt;p&lt;/i&gt; = .270, ES = 0.22, respectively). The MWMG showed improvements in pain (&lt;i&gt;p&lt;/i&gt; = .001, ES = 0.70) and RoM (right: &lt;i&gt;p&lt;/i&gt; = .0001, ES = 0.89; left: &lt;i&gt;p&lt;/i&gt; = .0001, ES = 0.99). The SG also showed improvements in pain (&lt;i&gt;p&lt;/i&gt; = .0001, ES = 0.76) and RoM (right: &lt;i&gt;p&lt;/i&gt; = .0001, ES = 0.49; left: &lt;i&gt;p&lt;/i&gt; = .0001, ES = 0.35). PPT improvements were observed in the MWMG for right and left trapezius (&lt;i&gt;p&lt;/i&gt; = .0001, ES = 1.21; &lt;i&gt;p&lt;/i&gt; = .040, ES = 0.43, respectively), whereas no significant changes occurred in the SG (&lt;i&gt;p&lt;/i&gt; = .713, ES = 0.03; &lt;i&gt;p&lt;/i&gt; = .839, ES = 0.01, respectively). The mobilization with movement technique leads to significant immediate improvements in muscle stiffness and pain-related parameters in individuals with chronic neck pain.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Analay Akbaba Yıldız, Özdemir Ayşem Ecem, Bali Kübra, Yalçın Ecem</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Physiotherapy theory and practice</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Humans, Double-Blind Method, Neck Pain, Range of Motion, Articular, Female, Adult, Male, Middle Aged, Pain Measurement, Pain Threshold, Treatment Outcome, Neck Muscles, Chronic Pain</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/40050244</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>39979944</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EMMATKA trial: the effects of mobilization with movement following total knee arthroplasty in women: a single-blind randomized controlled trial.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mobilization with Movement (MWM) is an examination and management approach for correcting the intra-articular translational and rotational movements to facilitate the active physiological movement. The study aimed to determine the effects of MWM on Total Knee Arthroplasty (TKA) using a randomized controlled trial (RCT) design. The trial is registered (ISRCTN ref: 13,028,992). A blinded examiner assessed patients at pre-surgical (before TKA), post-surgical (at 3-weeks post-TKA), 6-weeks and 6-months post-TKA. Participants were randomly assigned to receive MWM (six sessions, between 3 and 6 weeks post-TKA) plus standard rehabilitation (intervention group) or standard rehabilitation alone (control group) of outpatient rehabilitation including range of motion and strengthening exercises, cycling, gait and stair training. Outcome measures were range of motion (goniometer), pain (visual analogue scales), physical function (Timed Up and Go (TUG)), a 15-m walk test, and health status (Western Ontario and McMaster (WOMAC) Osteoarthritis Index). Change in outcome measures from post-surgical to 6 weeks and 6 months post-TKA were compared between groups. The primary outcome was change in knee flexion range of motion at 6 weeks. 84 women scheduled for TKA were randomly allocated to intervention (n = 42) or control (n = 42); mean ± (SD) age 65.1 ± 7.4 and 66.8 ± 8.9 years, respectively. The intervention group demonstrated significantly greater increase in knee flexion at both 6 weeks (median (IQR) + 10.00&lt;sup&gt;0&lt;/sup&gt; (20.00&lt;sup&gt;0&lt;/sup&gt;) compared with + 2.50&lt;sup&gt;0&lt;/sup&gt; (6.25&lt;sup&gt;0&lt;/sup&gt;) in the control group) and 6 months (+ 12.50&lt;sup&gt;0&lt;/sup&gt; (15.00&lt;sup&gt;0&lt;/sup&gt;) and + 5.00&lt;sup&gt;0&lt;/sup&gt; (10.00&lt;sup&gt;0&lt;/sup&gt;) respectively) (both p &lt; 0.05). There were no differences between groups in secondary outcomes. Introducing MWM for TKA rehabilitation has greater benefits for women post-TKA in increasing knee joint flexion range of motion than the standard rehabilitation programs in the short and medium-term. This evidence-based approach offers a promising adjunctive intervention for optimizing recovery and rehabilitation process following TKA in women. Clinicians should consider including MWM approach in post-TKA rehabilitation programs. I.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Alsiri Najla, Alshatti Sharifa A, Al-Saffar Maryam, Bhatia Rashida S, Fairouz Fatemah, Palmer Shea</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Journal of orthopaedic surgery and research</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Humans, Female, Arthroplasty, Replacement, Knee, Single-Blind Method, Aged, Range of Motion, Articular, Middle Aged, Movement, Treatment Outcome, Exercise Therapy, Osteoarthritis, Knee</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39979944</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>39919923</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The efficacy of Mulligan mobilization and corticosteroid injection on pain, functionality, and proprioception in rotator cuff tears: A randomized controlled trial.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Treatment of rotator cuff (RTC) tears commonly involves manual therapy, exercise, and injection methods. These treatments are typically administered together as components of a physical therapy intervention. However, it is not known which intervention is more effective. The objective of this study was to examine the impact of mobilization with movement (MWM) mobilization, a technique from Mulligan approaches, and corticosteroid (CS) injection on pain, functionality, and proprioception in cases of RTC tears. This was a single-blinded randomized clinical trial. Participants with RTC tears (n = 60) were divided into Mulligan mobilization (MM) and CS groups. The participants in the MM group performed mobilization with movement and a conventional exercise program; the CS group received a CS injection in addition to conventional exercises. The Visual Analog Scale, The Disabilities of the Arm, Shoulder, and Hand questionnaire, active range of motion (AROM), and joint position sense (JPS) were evaluated. The outcomes were analyzed using effect size, minimum clinically important difference, minimal detectable change, Wilcoxon test, and Mann-Whitney U test. Both groups significantly improved in all measured outcomes at 3 weeks. The MM group showed significantly better (p &lt; 0.05, Cohen d range 0.82-3.2) results in pain, AROM (Flexion, abduction, extension, external rotation, internal rotation), and proprioception (30° and 60° of flexion and abduction). Between-group differences in AROM were also clinically meaningful as they exceeded their MDC&lt;sub&gt;90&lt;/sub&gt; and minimum clinically important difference values. Although both of these treatment methods may be successful in the short-term management of chronic RTC, the MM approach combined with conventional exercises seems to be a more effective approach for improving shoulder pain, function, and proprioception in this patient population. NCT05933382.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Menek Burak, Menek Merve Yilmaz</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Journal of hand therapy : official journal of the American Society of Hand Therapists</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Humans, Female, Proprioception, Male, Rotator Cuff Injuries, Middle Aged, Single-Blind Method, Range of Motion, Articular, Pain Measurement, Aged, Musculoskeletal Manipulations, Adult, Adrenal Cortex Hormones, Treatment Outcome, Injections, Intra-Articular, Exercise Therapy</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39919923</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>39639272</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Knowledge and utilization of manual therapy in the management of knee osteoarthritis by physical therapists in Saudi Arabia: a cross-sectional study.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>The knowledge and utilization of manual therapy in treating knee osteoarthritis (OA) may help explain the effective utilization of manual therapy for managing knee OA. Little is known about the knowledge and utilization of manual therapy in the management of knee OA by physical therapists (PTs) in Saudi Arabia. The present study aimed to evaluate the knowledge and utilization of manual therapy by PTs in Saudi Arabia via a survey method. A cross-sectional study design was used. PTs working in various hospitals in Saudi Arabia participated. A 29-item questionnaire was developed based on previous studies. One hundred ninety-seven participants returned the completed questionnaire (response rate, 78.8%). Descriptive statistics were utilized to summarize and present the study participants' characteristics and responses. Approximately one-third (35.2%) of the participants did not receive any formal manual therapy training, whereas the others received formal manual therapy training in undergraduate (23.8%) or postgraduate (40.9%) studies. Only approximately one-third of the participants (29.9%) were qualified as certified manual therapy practitioners. Most participants (57%) reported using manual therapy according to the patient's condition. Most of the participants cited several treatment goals for manual therapy, including pain reduction (84.8%), improved range of motion (77.2%), increased mobility (58.2%), and improved function (55.4%). PTs in Saudi Arabia showed a positive attitude toward using manual therapy for treating knee OA. However, they suggested combining exercise and manual therapy as the best treatment option for knee OA. Not applicable.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Alghadir Ahmad H, Iqbal Zaheen A, Iqbal Amir</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>BMC public health</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Humans, Saudi Arabia, Cross-Sectional Studies, Osteoarthritis, Knee, Male, Female, Physical Therapists, Adult, Musculoskeletal Manipulations, Health Knowledge, Attitudes, Practice, Middle Aged, Surveys and Questionnaires</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39639272</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>39633647</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Effectiveness of multimodal active physiotherapy for chronic knee pain: a 12-month randomized controlled trial follow-up study.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Active physiotherapy (APT) embraces a patient-centered approach, prioritizing self-management within the biopsychosocial model and involving active patient movements. Beyond structured exercise, APT incorporates pain neuroscience education, Mulligan Mobilization (MWM), and active myofascial release techniques to integrate sensory-motor information for functional recovery and pain relief. This study aims to rigorously compare the effectiveness of APT &lt;i&gt;versus&lt;/i&gt; conventional physical therapy (CPT) on pain and functional outcomes in patients with chronic knee pain. Eighty-seven patients with symptomatic and radiographically confirmed knee pain were included in this 12-month follow-up of a randomized controlled trial, conducted at a national institute and a rehabilitation clinic. Patients were randomized to either APT (n = 44) or CPT (n = 43). The APT protocol integrated pain neuroscience education, MWM, active myofascial release techniques, and structured exercises focusing on flexibility, stability, neuromuscular control, and coordination. The CPT protocol included health education, laser therapy, ultrasound therapy, and exercise. Both interventions were performed for 60 min twice a week for 3 months. The primary outcome was the Knee Injury and Osteoarthritis Outcome Score-4 domain version (KOOS4). Secondary outcomes included pain intensity (VAS), KOOS-pain, activities of daily living (ADL), function in sport and recreation (Sports/Rec), knee-related quality of life, global rating of change (GROC), quality of life (SF-36), Tampa Scale for Kinesiophobia (TSK), and functional performances measured at different intervals. Intention-to-treat analyses were performed. Of the 87 patients, 70 (80.5%) completed the 12-month follow-up. KOOS4 improved more in the APT group (16.13; 95% CI, 10.39-21.88) than in the CPT group (11.23; 95% CI, 5.42-17.04). APT showed additional improvement in KOOS4 compared to CPT (2.94; 95% CI: 0.04 to 5.85, &lt;i&gt;p =&lt;/i&gt; 0.047). The VAS difference was -3.41 mm (95% CI: -6.40 to -0.43, &lt;i&gt;p&lt;/i&gt; = 0.025), favoring APT. APT also showed more improvements in KOOS-pain, KOOS-ADL, KOOS-Sports/Rec, and TSK (&lt;i&gt;p &lt;&lt;/i&gt; 0.05). No differences between groups were observed in GROC and SF-36. APT significantly improved most functional performance variables compared to CPT (&lt;i&gt;p &lt;&lt;/i&gt; 0.05). Active Physiotherapy outshines conventional physical therapy by delivering more substantial reductions in pain intensity and marked enhancements in function among patients with knee pain. This distinctive efficacy underscores the invaluable role of APT in the management of chronic knee pain. By actively involving patients in their recovery journey, APT not only fosters superior results but also emphasizes the critical need to integrate these advanced therapeutic strategies into everyday clinical practices.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cui Xinwen, Zhao Peng, Guo Xuanhui, Wang Jialin, Han Tianran, Zhang Xiaoya, Zhou Xiao, Yan Qi</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Frontiers in physiology</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39633647</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>39630775</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Effectiveness of mobilization with movement in patients operated for distal radius fracture: a single-blinded, randomized controlled study.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BACKGROUND: There are limited data on the use of Mulligan's mobilization with movement technique in patients who underwent surgery for distal radius fracture. AIMS: This study aimed to evaluate the effectiveness of adding Mulligan's mobilization with movement to the conventional exercise program for those who underwent open reduction and volar plate application due to distal radius fracture. This randomized controlled, single-blind study was conducted with 53 patients who had been operated on for distal radius fracture. The patients were divided into two groups, the mobilization with movement group and the control group. Patients in the mobilization with movement group were mobilized using Mulligan's mobilization with movement technique in addition to the rehabilitation program used in the control group. The degree of volar inclination and radial inclination were recorded. Radial height was measured in millimeters. Ulnar variance was recorded. Perimeter was measured using the Figure of Eight method. The range of motion of the joint was measured by goniometry. Hand grip strength was measured with Jamar® hand dynamometer, and pinch grip was measured with a pinch meter. The Patient-Rated Wrist Evaluation questionnaire was used to assess functionality. There is no statistically significant difference identified between the groups (p&gt;0.05). The intra-group changes in the data of the groups were found to be statistically significant in visual analog scale, range of motion, pinch grip, hand grip, and Patient-Rated Wrist Evaluation parameters (p&lt;0.05). There was a statistically significant difference between the mobilization with movement group and the control group for pronation value and hand grip strength value in measurements (p&lt;0.05). XThe mobilization with movement had no additive effect on parameters other than hand grip strength and pronation.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Horoz Levent, Cigdem-Karacay Basak, Ceylan Ismail, Alkan Halil</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Revista da Associacao Medica Brasileira (1992)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Humans, Female, Single-Blind Method, Male, Radius Fractures, Middle Aged, Range of Motion, Articular, Hand Strength, Treatment Outcome, Adult, Aged, Exercise Therapy, Recovery of Function, Wrist Fractures</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39630775</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>39593689</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The effects of the addition of Mulligan mobilization with movement to exercise on elbow pain and function associated with lateral elbow tendinopathy.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mulligan mobilization with movement (MWM) and eccentric exercise (EE) have been shown to be effective for the treatment of chronic lateral elbow tendinopathy (LET). However, the addition of MWM to EE effects on LET remained unknown. The objective of the study was to determine the effects of adding of Mulligan mobilization with movement to eccentric exercise for the treatment of LET. In this quasi-experimental study, thirty participants with unilateral LET were assigned into two groups: 15 in MWM (received MWM + EE) (7 M and 8 F, mean age 36.8 ± 8.3 years) and 15 in EE (9 M and 6 F, mean age 46 ± 8.1 years). Both groups received education about painful activities and eccentric exercise, while the MWM group received MWM with the same eccentric exercise as the EE group. The visual analog scale (VAS) and the patient-rated tennis elbow evaluation (PRTEE) were used to assess pain and upper limb function, respectively, at baseline and at the end of 4 weeks. The data was analyzed using an independent t-test and a paired t-test. There was no significant difference (p &gt; 0.05) between groups at baseline. At the end of 4 weeks, significant and clinically meaningful improvements in pain and function were observed for both groups (p &lt; 0.001); however, MWM group showed much better results in VAS (p &lt; 0.001, d = 1.3) and PRTEE (p &lt; 0.001, d = 5.2) CONCLUSION: This study showed that adding MWM to eccentric exercise resulted in enhanced pain reduction and improved function of the upper limb.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Syed Anayat Ullah, Darain Haider, Rana Mashaal</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Journal of bodywork and movement therapies</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Humans, Male, Female, Adult, Middle Aged, Exercise Therapy, Elbow Tendinopathy, Tennis Elbow, Pain Measurement, Range of Motion, Articular</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39593689</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>39516846</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>"Investigating the combined effects of scapular-focused training and Mulligan mobilization on shoulder impingement syndrome" a three-arm pilot randomized controlled trial.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>To assess whether the combination of scapular-focused training and mulligan mobilization (SFTMM) improves pain and proprioception compared to scapular-focused training (SFT) and a control group in female rock climbers with shoulder impingement syndrome (SIS). Three-arm randomized controlled trial (RCT). Outpatient setting. Individuals were randomly assigned to SFTMM, SFT alone, and control group. 8 weeks of SFTMM and SFT. Outcome measures were pain and proprioception. The results revealed significant differences in pain scores and proprioception among female rock climbers with SIS who participated in SFTMM, SFT, and a control group (F(2, 32) = 81.01, p = 0.001, η2 = 0.83 for pain scores; F(2, 32) = 178.2, p = 0.001, η2 = 0.91 for proprioception scores). Post-hoc tests via the Bonferroni test indicated that both SFTMM and SFT significantly reduced pain levels (p = 0.001) and improved proprioception levels (p = 0.001) compared with the control group. There was no significant difference in pain scores and proprioception between the SFTMM group and the SFT group (p &gt; 0.05). In conclusion, the study indicates that SFTMM significantly reduces pain and improves proprioception in female rock climbers with SIS, as shown by notable changes compared to the control group. However, no statistically significant difference was found between the SFTMM (combined intervention) and SFT alone. Therefore, while the incorporation of SFT and MM shows promise; further research is needed to fully understand its long-term benefits and clinical implications. The study was approved at Ethics. ac.ir, code: IR.SSRC.REC.1402.170 on 2023-10-22.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Zanjani Bita, Shojaedin Seyed Sadredin, Abbasi Hamed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>BMC musculoskeletal disorders</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Humans, Female, Shoulder Impingement Syndrome, Pilot Projects, Adult, Scapula, Proprioception, Exercise Therapy, Middle Aged, Treatment Outcome, Pain Measurement, Mountaineering</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39516846</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>39466747</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Effects of upper thoracic Mulligan mobilization on pain, range of motion and function in patients with mechanical neck pain: A randomized placebo-controlled trial.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>This study aimed to assess the impact of Mulligan Reverse Natural Apophyseal Glides (RNAGS) applied to the upper thoracic region on pain, movement limitation, and function in individuals with mechanical neck pain. Conducted between January 2021 and May 2021, the study involved 69 participants randomly assigned to a sham group, physiotherapy group, and Mulligan group. A two-week, 11-session treatment program was administered with shared physiotherapy interventions and stretching exercises to all groups. The Mulligan group received additional mobilization with the Mulligan RNAGS technique. The sham group received sub-standard Mulligan mobilization. Outcome measures included Range of Motion (ROM), Visual Analogue Scale (VAS), and Neck Disability Index (NDI). No baseline differences were found in measurements among the groups. After the intervention, all groups showed increased ROM and decreased VAS and NDI scores (p&lt;0.001). The Mulligan group exhibited significantly greater improvement in VAS, ROM, and NDI compared to other groups (p&lt;0.001). The sham group demonstrated greater improvement in NDI and extension ROM compared to the physiotherapy group (p&lt;0.001). Mulligan RNAGS technique in the upper thoracic region proved beneficial for pain relief, range of motion, and functionality in mechanical neck pain. Long-term effects warrant further exploration through population-based studies.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Cevik Ramazan, Pala Omer Osman</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PloS one</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Humans, Range of Motion, Articular, Male, Female, Neck Pain, Adult, Middle Aged, Physical Therapy Modalities, Pain Measurement, Treatment Outcome</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39466747</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>39340509</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Effectiveness of Mulligan Mobilization Technique and Core Stabilization Exercises in Female Patients With Knee Osteoarthritis: A Randomized Controlled Single-Blind Study.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The aim of this study was to compare the effectiveness of the Mulligan mobilization (MM) technique and Core stabilization (CS) exercises added to the conventional physiotherapy (CP) program in female patients with knee osteoarthritis (KOA). The study included 42 female patients diagnosed with bilateral KOA. Participants were randomly divided into 3 groups as CP group (mean age: 57.79 ± 7.43 years), MM group (mean age: 56.14 ± 6.95 years), and CS group (mean age: 54.36 ± 6.56 years). They were divided into 3 groups and treated 3 sessions per week for 4 weeks. Pain intensity, range of motion (ROM), and muscle strength were evaluated with visual analog scale, universal goniometer, and handheld dynamometer, respectively. Balance, aerobic capacity, and functional level were assessed with 30-second sit-to-stand test, 6-minute walk test, and Western Ontario and McMaster Universities Osteoarthritis Index. The quality of life of the participants was evaluated with the Nottingham Health Profile. After treatment, significant improvement was achieved in the all parameters evaluated in the groups (P &lt; .05). CS was found to be more effective in reducing resting pain intensity than the other two treatment approaches (P = .001). It was observed that MM technique increased knee flexion ROM more (P = .001). There was no superiority of MM group and CS group over each other in balance, functional level, aerobic capacity, and quality of life assessments (P &gt; .05). Our study showed that CP, MM technique, and CS exercises were effective treatment approaches in the management of KOA in female patients. Results revealed that the MM technique was more effective in increasing knee flexion ROM, and the CS exercise was more effective in reducing resting pain intensity in female patients with KOA.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Buke Meryem, Unver Fatma, Sekeroz Serbay, Oztekin Saadet Nur Sena</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Journal of manipulative and physiological therapeutics</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Humans, Female, Osteoarthritis, Knee, Middle Aged, Exercise Therapy, Single-Blind Method, Range of Motion, Articular, Treatment Outcome, Pain Measurement, Muscle Strength, Aged, Quality of Life</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39340509</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>39257326</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Manual therapy plus sexual advice compared with manual therapy or exercise therapy alone for lumbar radiculopathy: a randomized controlled trial.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>The biopsychosocial approach to managing low back pain (LBP) has the potential to improve the quality of care for patients. However, LBP trials that have utilized the biopsychosocial approach to treatment have largely neglected sexual activity, which is an important social component of individuals with LBP. The objectives of the study are to determine the effects of manual therapy plus sexual advice (MT+SA) compared with manual therapy (MT) or exercise therapy (ET) alone in the management of individuals with lumbar disc herniation with radiculopathy (DHR) and to determine the best sexual positions for these individuals. This was a single-blind randomized controlled trial. Fifty-four participants diagnosed as having chronic DHR (&gt;3 months) were randomly allocated into three groups with 18 participants each in the MT+SA, MT and ET groups. The participants in the MT+SA group received manual therapy (including Dowling's progressive inhibition of neuromuscular structures and Mulligan's spinal mobilization with leg movement) plus sexual advice, those in the MT group received manual therapy only and those in the ET group received exercise therapy only. Each group received treatment for 12 weeks and then followed up for additional 40 weeks. The primary outcomes were pain, activity limitation, sexual disability and kinesiophobia at 12 weeks post-randomization. The MT+SA group improved significantly better than the MT or ET group in all outcomes (except for nerve function), and at all timelines (6, 12, 26, and 52 weeks post-randomization). These improvements were also clinically meaningful for back pain, leg pain, medication intake, and functional mobility at 6 and 12 weeks post-randomization and for sexual disability, activity limitation, pain catastrophizing, and kinesiophobia at 6, 12, 26, and 52 weeks post-randomization (p&lt;0.05). On the other hand, many preferred sexual positions for individuals with DHR emerged, with "&lt;i&gt;side-lying&lt;/i&gt;" being the most practiced sexual position and "&lt;i&gt;standing&lt;/i&gt;" being the least practiced sexual position by females. While "&lt;i&gt;lying supine&lt;/i&gt;" was the most practiced sexual position and "&lt;i&gt;sitting on a chair&lt;/i&gt;" was the least practiced sexual position by males. This study found that individuals with DHR demonstrated better improvements in all outcomes when treated with MT+SA than when treated with MT or ET alone. These improvements were also clinically meaningful for sexual disability, activity limitation, pain catastrophizing, and kinesiophobia at long-term follow-up. There is also no one-size-fits-all to sexual positioning for individuals with DHR.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Danazumi Musa Sani, Adamu Isa Abubakar, Usman Musbahu Hamisu, Yakasai Abdulsalam Mohammed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Journal of osteopathic medicine</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Humans, Female, Radiculopathy, Male, Exercise Therapy, Single-Blind Method, Musculoskeletal Manipulations, Adult, Middle Aged, Lumbar Vertebrae, Treatment Outcome, Low Back Pain, Sexual Behavior, Intervertebral Disc Displacement, Combined Modality Therapy</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39257326</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>39189938</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The Clinical Significance of Mulligan's Mobilization with Movement in Shoulder Pathologies: A Systematic Review and Meta-Analysis.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;&lt;i&gt;Background:&lt;/i&gt;&lt;/b&gt; Mulligan's mobilization with movement (MWM) is a manual therapy technique designed to address musculoskeletal pain and joint mobility. Despite immediate reported improvements by patients, the clinical significance of MWM compared with other interventions remains uncertain. &lt;b&gt;&lt;i&gt;Objective:&lt;/i&gt;&lt;/b&gt; To assess the clinical effectiveness of MWM for shoulder pathologies compared with other treatment methods. &lt;b&gt;&lt;i&gt;Methods:&lt;/i&gt;&lt;/b&gt; The databases PubMed, Web of Science, Cochrane Library, Scopus, and the Physiotherapy Evidence Database (PEDro) were searched up to June 2024. Inclusion criteria were limited to randomized controlled trials published in English and Turkish languages, focusing on the MWM technique for shoulder pathologies. Two independent reviewers evaluated methodological quality based on the PEDro scale. Outcome data were analyzed for pain, function, and range of motion (ROM) using SPSS Statistics 29.0. &lt;b&gt;&lt;i&gt;Results:&lt;/i&gt;&lt;/b&gt; Twenty-seven studies (1157 participants) were included. MWM demonstrated statistical superiority in function (&lt;i&gt;MD = -11.24&lt;/i&gt;, 95% CI: [-18.33, -4.16], &lt;i&gt;p&lt;/i&gt; = 001) and shoulder flexion and abduction ROM compared with other mobilization techniques. There was a significant MD in pain intensity, which was -1.55 cm (95% CI: [-2.60, -0.51], &lt;i&gt;p&lt;/i&gt; = 0.00), with high heterogeneity (&lt;i&gt;I&lt;/i&gt;&lt;sup&gt;2&lt;/sup&gt; = 93%), favoring MWM in comparison with control group. MWM was significantly better for shoulder abduction ROM in comparison with physical therapy interventions (&lt;i&gt;MD = -14.44&lt;/i&gt;, 95% CI: [1.98, 26.90], &lt;i&gt;p&lt;/i&gt; = 0.02) with high heterogeneity (&lt;i&gt;I&lt;/i&gt;&lt;sup&gt;2&lt;/sup&gt; = 90%) and control group (SMD = 56.67, 95% CI: [7.71, 111.63], &lt;i&gt;p&lt;/i&gt; = 0.02) with high heterogeneity (&lt;i&gt;I&lt;/i&gt;&lt;sup&gt;2&lt;/sup&gt; = 96%). However, clinical significance was not consistently achieved. &lt;b&gt;&lt;i&gt;Conclusions:&lt;/i&gt;&lt;/b&gt; Although some statistical significance was found when comparing MWM with other her treatment methods, it was observed that most of the statistically significant data did not reach clinical significance. Upon closer examination, outcome measures that showed clinical significance, either the interventions in the comparison group were inadequate, not evidence-based, or the improvements within the group were not logical.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Çelik Derya, Van Der Veer Pınar, Tiryaki Pelin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Journal of integrative and complementary medicine</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Humans, Clinical Relevance, Musculoskeletal Manipulations, Randomized Controlled Trials as Topic, Range of Motion, Articular, Shoulder, Shoulder Pain</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39189938</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>39104993</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Crushing Consequences: A Case Report on the Rehabilitation of a Middle Phalangeal Fracture in an Industrial Incident.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hand injuries, particularly fractures involving the phalanges and metacarpals, are common occurrences in various settings, including industrial environments. Prompt and effective management of these injuries is crucial to minimize long-term disability and facilitate return to work. This case report focuses on the rehabilitation of a middle phalangeal fracture in an industrial worker following Kirschner wire (K-wire) fixation. The patient, a 24-year-old male, sustained the injury while operating an electric stamping machine. Emergency surgery was performed to stabilize the fracture, and subsequent physiotherapy was initiated due to persistent difficulties in hand function. The rehabilitation protocol aimed to address pain, improve range of motion, and enhance grip strength through passive range of motion exercises, movement with mobilization techniques, blocking exercises, and grip strengthening exercises. Mulligan's mobilization with movement (MWM) concept was incorporated to facilitate rapid pain relief and movement restoration. Follow-up assessments after four weeks of rehabilitation revealed significant improvements in pain levels, range of motion, strength, and overall quality of life. The case underscores the importance of timely intervention and comprehensive rehabilitation strategies in managing traumatic hand injuries in industrial settings, aiming to optimize treatment outcomes and promote successful return to work.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Vikhe Chaitali S, Ramteke Swapnil U, Jaiswal Pratik R</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39104993</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>39092393</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A Case Report Emphasizing the Advantageous Effect of Mulligan Mobilization Technique in the Management of Rotator Cuff Syndrome to Enhance Functional Recovery in a 65-Year-Old Farmer.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Adults with shoulder pain often have partial rotator cuff injuries (RCIs) as the underlying cause. RC partial tears are one of the common conditions that can have a major influence on a wide range of people, including sportspeople, workers, and sedentary adults with rotator cuff syndrome (RCS). Any injury, disease, or deteriorating condition that affects the shoulder's RC muscles and tendons is recognized as RCS. Subacromial bursitis, RC tendonitis, subacromial impingement syndrome (SIS), rotator cuff tears (RCTs), etc., are a few disorders linked to RCS. For partial RCT, nonoperative treatment options include physical therapy, anti-inflammatories, analgesics, medication, rest or activity adjustments, and corticosteroid injections. We present the case of a 65-year-old male farmer by occupation, suffering from an RCI on the right side. Following a history of trauma to the right shoulder from a collision with a bull on his farm, the patient complained of pain and limitations in his right shoulder joint. The goal of the rehabilitation program was to maximize the patient's recovery through pain management, range-of-motion (ROM) restoration, muscle strength building, and functional activities. To improve muscular strength and preserve the ROM, strengthening exercises and isometrics were all incorporated into the rehabilitation regimen at the same time. The patient's progress was monitored at scheduled times during rehabilitation using the disabilities of arm, shoulder, and hand (DASH) score, visual analog scale (VAS), goniometer for normal ROM, and the upper extremity functional scale (UEFS). In this case study, the care and recovery of a patient with RC tendinopathy who received physical therapy are examined.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sonone Samiksha V, Patil Deepali S</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39092393</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>39028043</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>The effects of ankle mulligan mobilisation in children with cerebral palsy: A randomized single blind control study.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>To assess the impact of range of motion changes before and after Mulligan mobilisation with ankle movement interventions on the daily lives of children with diplegic cerebral palsy. The single blind randomised controlled study was conducted from July 30, 2022, to January 10, 2023, at 3 rehabilitation centres in Hebron, Palestine, after approval from the ethics review committee of Eastern Mediterranean University, Northern Cyprus, and comprised children with cerebral palsy, who were randomised into intervention group IG and control group CG. All the subjects received regular physiotherapy sessions, overseen by their parents, while those in group IG received mobilisation with ankle movement treatment 3 times per week for 4 weeks. Post-intervention assessment of ankle range of motion, balance, functional performance and quality of life was done using a goniometer, the timed up and go test, 88-item gross motor function measure, 6-minute walk test and the cerebral palsy quality of life questionnaire. Data was analysed using SPSS 24. Of the 64 patients, 40(63%) were girls, and 24(37%) were boys. The overall age range was aged 4-12 years. There were 32(50%) patients in each of the two groups. Mobilisation with movement had a significant effect on active and passive range of motion for the left and right ankles (p&lt;0.05) as well as on balance, gross motor function and quality of life (p&gt;0.05). However, mobilisation with movement had no significant effect on the the distance covered during the 6-minute walk test (p&gt;0.05). Mobilisation with movement had a significant impact on active and passive ankle range of motion, balance and quality of life in diplegic children with cerebral palsy, but it had no impact on gait function. The study was registered at the United States National Institutes of Health (ClinicalTrials.gov) with registration number NCT05500924.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ragheb Abushameh Ratib Shaban, Topcu Zehra Guchan, Tunal Ayse Nur, Amro Akram, Arab Azzam Al</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>JPMA. The Journal of the Pakistan Medical Association</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Humans, Cerebral Palsy, Female, Male, Single-Blind Method, Child, Range of Motion, Articular, Quality of Life, Child, Preschool, Ankle Joint, Physical Therapy Modalities, Postural Balance, Ankle</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/39028043</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2024-Jul</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>38929735</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Outcomes of Mulligan Concept Applications in Obese Individuals with Chronic Mechanical Low Back Pain: A Randomized Controlled Trial.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Various treatment modalities have been employed for mechanical low back pain (MLBP), but evidence of their efficacy varies greatly. Objectıve: This randomized controlled trial aimed to assess the outcomes of Mulligan concept applications, including sustained natural apophyseal glides (SNAGS) and natural apophyseal glides (NAGS), in obese patients with MLBP. The study, conducted between January 2021 and June 2022 at a tertiary hospital, involved randomizing patients into two groups. Both groups underwent six sessions of stretching and strengthening exercises every other day. The Mulligan group received additional intervention with SNAG and NAGS techniques. Measurements were made regarding the Visual Analog Scale (VAS) score, Oswestry Disability Index (ODI) score and range of motion (ROM) for the patients' MLBP level. Post-interventions, both groups exhibited positive changes in flexion ROM, extension ROM, right and left rotation ROM, right and left lateral flexion ROM, VAS score, and ODI score compared to pre-intervention (&lt;i&gt;p&lt;/i&gt; &lt; 0.001 for both groups and variables). The Mulligan group showed a higher increase in ROM and a more significant decrease in VAS and ODI scores. Conclusıons: Mulligan mobilization techniques prove significantly beneficial for enhancing ROM in all directions, reducing pain levels, and alleviating disability in obese individuals with MLBP.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Cankaya Muhammed Safa, Pala Omer Osman</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Life (Basel, Switzerland)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38929735</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>38902195</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mulligan manual therapy added to exercise improves headache frequency, intensity and disability more than exercise alone in people with cervicogenic headache: a randomised trial.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>What is the effect of a 4-week regimen of Mulligan manual therapy (MMT) plus exercise compared with exercise alone for managing cervicogenic headache? Is MMT plus exercise more effective than sham MMT plus exercise? Are any benefits maintained at 26 weeks of follow-up? A three-armed, parallel-group, randomised clinical trial with concealed allocation, blinded assessment of some outcomes and intention-to-treat analysis. Ninety-nine people with cervicogenic headache as per International Classification of Headache Disorders (ICHD-3). Participants were randomly allocated to 4 weeks of: MMT with exercise, sham MMT with exercise or exercise alone. The primary outcome was headache frequency. Secondary outcomes were headache intensity, headache duration, medication intake, headache-related disability, upper cervical rotation range of motion, pressure pain thresholds and patient satisfaction. Outcome measures were collected at baseline and at 4, 13 and 26 weeks. MMT plus exercise reduced headache frequency more than exercise alone immediately after the intervention (MD between groups in change from baseline: 2 days/month, 95% CI 2 to 3) and this effect was still evident at 26 weeks (MD 4 days, 95% CI 3 to 4). There were also benefits across all time points in several secondary outcomes: headache intensity, headache duration, headache-related disability, upper cervical rotation and patient satisfaction. Pressure pain thresholds showed benefits at all time points at the zygapophyseal joint and suboccipital areas but not at the upper trapezius. The outcomes in the sham MMT with exercise group were very similar to those of the exercise alone group. In people with cervicogenic headache, adding MMT to exercise improved: headache frequency, intensity and duration; headache-related disability; upper cervical rotation; and patient satisfaction. These benefits were not due to placebo effects. CTRI/2019/06/019506.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Satpute Kiran, Bedekar Nilima, Hall Toby</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Journal of physiotherapy</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Humans, Male, Female, Post-Traumatic Headache, Exercise Therapy, Adult, Middle Aged, Musculoskeletal Manipulations, Treatment Outcome, Range of Motion, Articular</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38902195</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>38876630</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>The effect of mulligan mobilization technique application in addition to conventional physiotherapy on pain and joint range of motion in people with neck pain.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>To evaluate the effect of the Mulligan mobilization technique on pain intensity and range of motion in individuals with neck pain. Forty individuals with mechanical neck pain were enrolled in the study. The patients were randomly divided into 2 groups and a total of 10 sessions of treatment were administered to all 2 groups for 2 weeks, 5 days a week. Mulligan mobilization technique, electrophysical agents, active range of motion, and stretching exercises were carried out in the Mulligan group. In contrast, only electrophysical agents and exercises were applied to the conventional physiotherapy group. Range of motion (ROM) of the neck, Visual Analog Scale (VAS), Neck Pain and Disability Scale (NPDS), and Short-Form 36 Health Survey (SF-36) were used for evaluation. Statistical analyses were done to compare the amounts at the baseline and immediately after treatment. Statistically significant improvements were found in the post-treatment ROM, VAS, NPDS values in both groups (p &lt; 0.05). When the differences were compared, the results of the Mulligan group were significantly better than the conventional physiotherapy group (p &lt; 0.05). There was no significant difference between the groups in terms of SF-36 parameters (p &gt; 0.05). This study showed that the Mulligan mobilization technique plus conventional physiotherapy is more effective than conventional physiotherapy in increasing joint range of motion, reducing pain, and reducing neck disability. ClinicalTrials.gov (NCT05074576).</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ozlu Ozge, Sahin Mustafa</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Journal of bodywork and movement therapies</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Humans, Neck Pain, Range of Motion, Articular, Female, Male, Adult, Middle Aged, Physical Therapy Modalities, Pain Measurement, Exercise Therapy, Exercise Movement Techniques, Disability Evaluation</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38876630</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>38779251</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Management of Low Back Pain With Concurrent Hamstring Tightness: A Case Report Highlighting the Efficacy of Proprioceptive Neuromuscular Facilitation, Mulligan's Two-Leg Rotation Technique, and Exercise Regimen.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Low back pain (LBP) is a prevalent musculoskeletal issue characterized by discomfort in the lumbosacral region. LBP localized between the 12th thoracic vertebra and inferior gluteal folds is common and often lacks a clear etiology. Various factors contribute to LBP, including increased lumbar lordosis, diminished abdominal muscle strength, reduced back extensor muscle endurance, and flexibility limitations in the back extensors, iliopsoas, and hamstrings. Treatment modalities for LBP encompass surgical intervention, pharmacotherapy, lumbar injections, psychotherapy, chiropractic care, and physiotherapy, with manual therapy being a prominent approach. Physiotherapists employ a spectrum of manual techniques, including mobilization, manipulation, and massage, to address LBP. Hamstring flexibility plays a pivotal role in spinal mechanics, and tight or shortened hamstrings can exacerbate LBP. Mulligan's techniques, notably the two-leg rotation (TLR) technique, are valuable interventions for addressing hamstring tightness in cases of LBP. Proprioceptive neuromuscular facilitation (PNF) was also used to manage pain and improve strength. This case report outlines the management of a 32-year-old male presenting with LBP and hamstring tightness coupled with core muscle weakness. Through comprehensive assessment and physiotherapeutic interventions, significant improvements were observed in pain intensity, lumbar range of motion, disability, straight leg raise (SLR), and core muscle strength following a three-week physiotherapy intervention.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Tikhile Priya, Patil Deepali S, Jaiswal Pratik R</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38779251</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>38756306</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Physiotherapeutic Management for Acromioclavicular Joint Sprain With Volar Intercalated Segment Instability at the Wrist: A Case Report.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Among sports enthusiasts and young individuals, acromioclavicular (AC) joint injuries are highly prevalent. In this, we discussed the comprehensive assessment and management of a 22-year-old male patient who is a student by occupation and a recreational badminton player who presented with left shoulder and wrist pain following a road traffic accident. The study highlights the clinical findings, diagnostic assessment, and therapeutic interventions for the patient with volar intercalated segment instability and a grade 1 AC joint sprain. The methodology involves a case report of the patient's clinical evaluation, including range of motion, manual muscle testing, and diagnostic imaging. The patient was managed conservatively with physiotherapy interventions, including Mulligan's movement with mobilization, cryotherapy, light amplification by stimulated emission of radiation, and progressive exercises. The results of the study demonstrate the successful implementation of a multidisciplinary conservative management approach for alleviating pain, restoring function, and promoting optimal recovery for the patient. The implications of the study underscore the significance of tailored physical therapy rehabilitation in the management of AC joint sprains and wrist instabilities.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Nathani Harsh R, Ramteke Swapnil U, Jaiswal Pratik R</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38756306</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38707100</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>The Therapeutic Efficacy of Ankle Mobilization and Advance Physiotherapy in Alleviating Heel Spur and Plantar Fasciitis: A Case Report.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Plantar fasciitis arises from progressive damage of the plantar fascia, which originates at the medial calcaneal tuberosity and associated perifascial tissues. The plantar fascia is made up of three segments that grow from the calcaneus and serve a crucial role in appropriate foot biomechanics. The plantar fascia itself is vital in supporting the arch and absorbing trauma. The heel spur is one of the most prevalent causes of foot discomfort. It is important to determine the most effective technique of therapy based on the emergence of pain at each step of the day. This case report describes the thorough rehabilitation of a 42-year-old mesomorphic female, a yoga instructor, and a recreational runner who presented with heel spur and plantar fasciitis symptoms. In addition to traditional therapy, the patient received advanced physical therapy with an emphasis on Mulligan joint mobilization to lessen discomfort and increase range of motion. The objective was to evaluate the effect of this intervention on several outcome measures, such as the visual analogue scale, balance test, foot functional scale, range of motion, and lower extremity functional scale. Targeted exercises and treatments were incorporated into the comprehensive rehabilitation plan to enhance foot function. The patient received the enhanced physiotherapy intervention well. The outcome measure showed notable gains. This case contributes greatly to our knowledge of the best physiotherapy treatments for those with plantar fasciitis and heel spurs.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Boob Manali A, Phansopkar Pratik, Somaiya Kamya J</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38707100</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38665699</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Integrated Rehabilitation Approach Utilizing Swiss Ball Training, Mulligan Taping, and Mobilization With Movement for Simultaneous Management of Sacroiliac Joint Dysfunction and Lateral Ankle Sprain in a Badminton Athlete: A Case Study.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>This case report details an integrated rehabilitation plan implemented for a professional badminton player who presented with issues of sacroiliac joint (SIJ) dysfunction and a lateral ankle sprain. The integrated approach aimed to address both musculoskeletal issues, considering their potential reciprocal influences on biomechanics and functional performance. The athlete underwent a thorough initial assessment, including clinical examination, imaging, and biomechanical analysis. Treatment began with targeted interventions for acute ankle sprain management, such as rest, ice, compression, and elevation (RICE) followed by progressive exercises to restore ankle stability and range of motion (ROM). Concurrently, a specialized program was devised to address the underlying sacroiliac joint dysfunction through manual therapy, therapeutic exercises, and core stabilization routines. Throughout the rehabilitation process, the focus remained on integrated exercises that targeted both the ankle and sacroiliac joint, promoting optimal neuromuscular coordination and joint function specific to badminton demands. Regular reassessments guided the progression of interventions, ensuring a personalized and athlete-centric approach. The positive outcome highlights the importance of a holistic rehabilitation strategy in managing complex musculoskeletal conditions in athletes, facilitating efficient recovery, and reducing the risk of recurrence. This case report highlights the effectiveness of an integrated approach in enhancing performance and preventing reinjury in badminton athletes facing multifaceted musculoskeletal challenges.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Shedge Saylee S, Ramteke Swapnil U, Samal Subrat</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38665699</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>38654798</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Physiotherapeutic Intervention Techniques for Knee Osteoarthritis: A Systematic Review.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Globally, knee osteoarthritis (KOA) is the leading cause of disability. The most prevalent complaints associated with KOA are knee pain, joint stiffness, and weakness in the muscles of the lower limbs. These symptoms impede movement and result in functional limitations. As a result, people with KOA have a lower quality of life. For all patient groups with knee OA, an effective rehabilitation program focuses on improving knee range of motion, isometric quadriceps strength, and productivity level while reducing discomfort. The American College of Rheumatology (ACR) categorization criteria for KOA, research on KOA physiotherapy, and reviews covering various physical therapy interventions, including exercise, physical modalities, and patient education, were used to narrow down the pool of 180 systematic reviews to 15 articles. Google Scholar, PubMed, the Cochrane Library, and EMBASE were the databases that were used. The following keyword combinations were included in our search: KOA and physiotherapy or interventions or exercises, strengthening and stretching, concentric and eccentric training. Through our analysis, we identified a few methods that, in addition to standard therapy, could be used in clinical settings for people with osteoarthritis in the knee. It has been shown that Mulligan, Pilates, Kinesiotaping, Aquatic Therapy, and other current therapies are effective. The study employed a broad range of results. This review concludes that rather than relying solely on conventional therapy, it is preferable to combine a number of the most current physiotherapy techniques with it.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Somaiya Kamya J, Samal Subrat, Boob Manali A</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38654798</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2024-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>38638770</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Efficacy of PowerBall Versus Mulligan Mobilization With Movement on Pain and Function in Patients With Lateral Epicondylitis: A Randomized Clinical Trial.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Background Lateral epicondylitis (LE), sometimes referred to as tennis elbow or lateral elbow tendinopathy (LET), is one of the most common repetitive stress disorders in the elbow joint. Often, this involves the attachment of the extensor carpi radialis brevis muscle. This study's primary focus is on treating people with LE, a condition that causes repetitive movements of the upper extremities. There is currently no research on how PowerBall gadget workouts affect the function and pain of individuals with lateral epicondylitis. Exercises using the "PowerBall device," which applies both intrinsic and extrinsic pressure to the wrist, elbow, and shoulder muscles, are thought to be beneficial forms of resistance training. It has been shown that there are improvements in strength, function, range of motion (ROM), discomfort, and quality of life (QOL). On the other side, it has been demonstrated that LE patients have reduced discomfort while using Mulligan Mobilization with Movement (MMWM). Methods The 50 patients with LE were split into two groups for the single-blinded, randomized clinical study after baseline assessment and randomization: Group A was the intervention group, and Group B was the conventional group. The "PowerBall device" exercise was provided to participants in Group A, and MMWM was given to those in Group B. Both groups can benefit from basic workouts and ultrasonography by following the prescribed routine. Quantification of pain, function, grip strength, and range of motion was done at the start and finish of therapy using the Visual Analogue Scale (VAS), Patient Rated Tennis Elbow Evaluation (PRTEE), portable dynamometer, and goniometer. Results After therapy, both groups showed considerable improvement (p&lt;0.05). Both descriptive and inferential statistics were employed in the data analysis. Numerous statistical tests were employed, such as the student's paired and unpaired t-test and the chi-square test. From a statistical and clinical perspective, Group A's outcomes were more significant. On the visual analog scale, there was a decrease in pain intensity for wrist and elbow mobility at rest (p&lt;0.0003), activity (p&lt;0.003), PRTEE (p&lt;0.001), grip strength (p&lt;0.03), and range of motion (p&lt;0.01). Both groups' assessments after rehabilitation indicated increases in pain and function; however, Group A (0.03) benefited more and saw early success with the PowerBall device. Conclusion Findings show that a three-week program incorporating resistance training exercises mediated by a "PowerBall device" enhances upper limb performance beyond traditional exercise treatment and increases grip strength, wrist extension strength, internal and external rotator concentric and eccentric strength. The findings and observations indicate that both groups have significantly improved.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Uttamchandani Shivani R, Phansopkar Pratik</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38638770</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>38618993</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Efficacy of Mulligan thoracic sustained natural apophyseal glides on sub-acromial pain in patients with sub-acromial impingement syndrome: a single-blinded randomized controlled trial.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>To investigate the effects of Mulligan thoracic sustained natural apophyseal glides (SNAGS) techniques and traditional exercises on pain, shoulder function, size of sub-acromial space, and shoulder joint range in patients with sub-acromial impingement syndrome. Seventy-four patients with sub-acromial impingement syndrome (25 to 40 years) joined this research and were allocated randomly into two equal groups; experimental group A (Mulligan SNAGS and exercise) and control group B (exercise only). All patients were assessed by visual analogue scale (VAS) for pain intensity, Shoulder Pain and Disability Index (SPADI) for shoulder function, plain x-ray for the size of sub-acromial space, and goniometer for shoulder range of motion (ROM). The measurements were performed at two intervals (baseline and after four weeks of intervention). After 4 weeks of intervention, there were statistically significant differences between groups, in favor of Mulligan SNAGS, on sub acromial space size, pain intensity, shoulder function, and shoulder joint range of motion (&lt;i&gt;p&lt;/i&gt; &lt; 0.05). In within-group analysis, there were also statistically significant differences between pre- and post-treatment in all measured variables (&lt;i&gt;p&lt;/i&gt; &lt; 0.05). Mulligan thoracic spine (SNAGS) mobilization into extension and traditional exercises improve sub acromial space size, pain intensity, shoulder function, and shoulder joint range of motion in patients with sub acromial impingement syndrome. It is recommended to mobilize the thoracic spine by mulligan SNAGS in the treatment of sub-acromial impingement syndrome.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Abu El Kasem Shimaa T, Alaa Fatma Alzahraa A, Abd El-Raoof Neveen A, Abd-Elazeim Alshaymaa S</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>The Journal of manual &amp; manipulative therapy</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Humans, Shoulder Impingement Syndrome, Adult, Male, Female, Range of Motion, Articular, Single-Blind Method, Pain Measurement, Shoulder Pain, Treatment Outcome, Exercise Therapy</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38618993</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>38606230</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unveiling the Efficacy of Physiotherapy Strategies in Alleviating Low Back Pain: A Comprehensive Review of Interventions and Outcomes.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Low back pain (LBP) presents a significant burden globally, affecting individuals of all ages, but it is more common in adults aged 30-60 years old and demographics including race, ethnicity, and socioeconomic status. Physiotherapy interventions are commonly employed to manage LBP due to their non-invasive nature and potential for addressing underlying biomechanical dysfunctions. This comprehensive review aims to evaluate the efficacy of various physiotherapy strategies in alleviating LBP, considering a range of interventions and their associated outcomes. Through a thorough examination of existing literature from January 2017 to October 2023, this review synthesises evidence on the effectiveness of interventions such as manual therapy, exercise therapy, electrotherapy modalities, and education-based approaches. The review also scrutinizes the comparative effectiveness of different physiotherapy modalities and their suitability for specific patient populations, considering factors such as chronicity, severity, and underlying pathology. By critically evaluating the evidence base, this review aims to provide insights into the most effective physiotherapy strategies for alleviating LBP, chronic low back pain (CLBP) and chronic nonspecific low back pain (CNLBP) and guiding clinical practice toward evidence-based interventions. The Visual Analogue Scale and Numerical Pain Rating Scale for pain, Oswestry Disability Index and Roland-Morris Disability Questionnaire for disability, Modified-Modified Schober Test for measurement of lumbar flexion and extension and static and dynamic balance for assessing postural stability and balance were among the measures used to foresee enhancements in pain, disability, balance, and LBP symptoms. Twenty-one studies that fulfilled the criteria for inclusion (aged 20 to 50 years and of both genders) were added to the review. Exercises for core stability, strengthening, orthosis (a medical device designed to support, align, stabilise, or correct musculoskeletal structures and functions), transcutaneous electrical nerve stimulation, heat massage therapy, interferential current (a form of electrical stimulation used in physical therapy), Mulligan's mobilization (a manual therapy technique), low-level laser therapy, and McGill stabilization exercises (core exercises) were among the therapeutic strategies. The McKenzie method (back exercises), ultrasound, sensory-motor training, Swiss ball exercises, and other techniques reduced pain and enhanced strength, balance, and ease of daily activities. Every therapeutic approach has an impact on recovery rates ranging from minimal to maximal. Conventional physical therapy is less effective than most recent advanced techniques like mobilisation and exercises. In summary, the integration of manual techniques, orthoses and alternative intervention strategies with conservative therapeutic approaches can effectively alleviate pain, enhance function and yield better overall outcomes. To get more information about the optimal dosage, therapeutic modalities and long-term effects of these treatments, more admirable research is required. This paper aims to expand the scientific discourse by exploring non-traditional physiotherapy interventions and assessing their efficacy in light of the rigorous standards set forth by the latest WHO guidelines.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Tikhile Priya, Patil Deepali S</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38606230</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>38567231</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>A Case Report of Sjögren's Syndrome and Rheumatoid Arthritis: The Role of Physiotherapy in Enhancing Quality of Life.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Rheumatoid arthritis (RA) is a systemic autoimmune disease with profound effects on joints and extra-articular organs. This case report explores the complex treatment approach for a 54-year-old female patient who is dealing with the dual diagnosis of RA and Sjogren's syndrome (SS). RA primarily involves joint inflammation and morning stiffness leading to significant disability, while SS, another autoimmune condition, manifests with autoantibodies and lymphocytic infiltration affecting exocrine glands. The patient presented with joint and low back pain, alongside reduced mobility, portraying a complex clinical picture. Physiotherapy played a crucial role in addressing the diverse symptoms exhibited by the patient. Treatment involved Mulligan mobilization targeting sacroiliac joint dysfunction, laser therapy for pain relief, and tailored exercises focusing on joint mobility and muscle strength. Progress was monitored using the Rheumatoid Arthritis Disease Activity Index (RADAI-5) and overall quality of life assessments. Significant improvements were observed post-rehabilitation including reduced pain levels, increased joint range of motion, increased muscle strength, and enhanced sacroiliac mobility. These positive outcomes highlight the efficacy of physiotherapy in managing autoimmune rheumatic disorders. Collaboration between healthcare professionals particularly rheumatologists and physiotherapists is essential for comprehensive patient care. This case emphasizes the importance of adopting a holistic approach to managing autoimmune disorders. Physiotherapy emerges as a pivotal component in alleviating symptoms and enhancing physical function underscoring its integration into the multidisciplinary care framework for individuals facing the challenges of autoimmune rheumatic disorders.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bhagwatkar Sawari S, Harjpal Pallavi, Ankar Prajyot</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38567231</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>38544636</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Integrative Approach of Conventional Physiotherapy, Mulligan's Mobilisation With Movement, and Plyometric Training in a Young Volleyball Athlete After Anterior Cruciate Ligament (ACL) Reconstruction: A Case Report.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>The requirements of volleyball include specialized, strategic, and acrobatic skills. In volleyball, it is thus essential to build maximal power and strength properly. Strengthening has been recommended as an effective means to avoid injuries and build muscle strength. It also enhances one's health in relation to performance in the game. Anterior cruciate ligament (ACL) tears are a common knee injury affecting athletes of all levels. A big problem with injury healing and getting back to sports is that there isn't a tried-and-true protocol or set of steps an athlete should follow following an ACL injury. Plyometric training focuses on the core, hip, and thigh muscles to help with appropriate lower limb alignment and recruiting of muscle. We present a 25-year-old male volleyball athlete who suffered from an ACL tear. This case report emphasises how important sports physiotherapy rehabilitation is for athletes. The case report advances the treatment of ACL injury by a multifaceted approach of Mulligan's mobilisation with movement and plyometric-based interventions.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jaiswal Pratik R, Ramteke Swapnil U, Samal Subrat</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38544636</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>38533161</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Effectiveness of Recent Physiotherapy Techniques Along With Conventional Physiotherapy Techniques in a Patient With Knee Osteoarthritis: A Case Report.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Osteoarthritis (OA), the most common joint disease, lowers quality of life, restricts social activity participation, and results in incapacity. Osteoarthritis is characterised by changes in subchondral bone, meniscus degeneration, cartilage loss, and synovial inflammation. Physiotherapy plays a vital role in maintaining the stability of this disease. Various treatment approaches have been shown in numerous studies to be successful in improving the condition of individuals with osteoarthritis in the knee. We are presenting a case of a 47-year-old woman who had bilateral osteoarthritis in her knees. We created a six-week treatment plan for this patient that incorporates a number of advanced therapy techniques, including Mulligan mobilisation, Kinesio taping, and plyometric exercise sessions. We created a thorough rehabilitation programme for our patient, who had osteoarthritis in her knee, and it worked incredibly well. We assessed the efficacy of our outcome measures using a variety of outcomes, including the Western Ontario and McMaster Universities Osteoarthritis Index (WOMAC), Knee Injury and Osteoarthritis Outcome Score (KOOS), visual analogue scale (VAS), range of motion (ROM), and manual muscle testing (MMT). It was found to be more beneficial to provide modern physiotherapeutic approaches in addition to a traditional physiotherapy course for improving the overall health and quality of life of the patient.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Somaiya Kamya J, Samal Subrat, Boob Manali A</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38533161</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>38234929</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>"Mulligan Bent Leg Raise" Technique in Avascular Necrosis.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>This case report examines the effectiveness of the "Mulligan bent leg raise" (MBLR) method for treating femoral head avascular necrosis (AVN). A professional physiotherapist directed a six-week rehabilitation program for a 37-year-old male patient with AVN that included this innovative physiotherapeutic method. According to radiographic results and standardized evaluations, the patient showed significant improvements in hip range of motion, functional ability, and pain levels. As a viable supplement to conventional rehabilitation techniques, the MBLR method has shown promise in improving joint function and reducing symptoms in individuals with acute compartment syndrome. The present study provides significant contributions to the discipline. It highlights the necessity for more investigation to examine the wider relevance and enduring effectiveness of this methodology in various population affected.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Karanjkar Samruddhi M, Dhage Pooja</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38234929</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>38222176</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Promoting Flexibility and Functionality in a Surgically Managed Tibial Fracture: A Case Report on Physiotherapeutic Interventions for Postoperative Stiffness.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>This case study explains the complete care of a 45-year-old male patient who had a high-impact road injury that resulted in a displaced proximal tibial fracture. Substantial soft tissue damage was discovered during the initial assessment, requiring careful thought before undergoing surgery. A customized physiotherapy program was instituted after an incremental strategy involving open reduction and internal fixation. The patient made a satisfactory functional recovery, regaining nearly normal mobility and going back to daily activities within 12 weeks despite difficulties encountered during the rehabilitation phase, including temporary postoperative complications. The present study underscores the significance of a multidisciplinary approach involving Mulligan mobilization in the effective management of intricate proximal tibial fractures. It also underscores the importance of meticulous surgical intervention and organized rehabilitation protocols in enhancing patient outcomes and regaining functional abilities to improve patients' quality of life.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Shende Krishnayani, Ratnani Grisha, Deodhe Nishigandha P, Gandhi Khushi M</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38222176</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>38068468</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Effect of Mobilization with Movement on Pain, Disability, and Range of Motion in Patients with Shoulder Pain and Movement Impairment: A Systematic Review and Meta-Analysis.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Shoulder pain is a disabling musculoskeletal disorder worldwide. Thus, it is important to identify interventions able to improve pain and disability. To investigate the effects of mobilization with movement (MWM) on pain, disability, and range of motion in patients with shoulder pain and movement impairment. A systematic search of different databases was performed. The systematic review protocol has been registered in PROSPERO (CRD42023404128). A random-effects model for meta-analysis was used to determine the mean difference (MD), standardized mean differences (SMD), and 95% confidence interval for the outcome of interest. Twenty-six studies were included. Of these, eighteen were included in the meta-analysis. MWM improved pain during movement with a moderate effect SMD of (-0.6; 95% confidence interval, -1.1 to -0.1, I&lt;sup&gt;2&lt;/sup&gt; = 0%; N = 66;) and shoulder abduction MD of (12.7°; 1.3 to 24.0; I&lt;sup&gt;2&lt;/sup&gt; = 73%; N = 90) compared to sham MWM in the short term (0-6 weeks). Combined MWM and conventional rehabilitation improved pain at rest, with a MD of (-1.2; -2.2 to -0.2; I&lt;sup&gt;2&lt;/sup&gt; = 61%; N = 100), and disability SMD of (-1.3; confidence interval -2.2 to -0.4; I&lt;sup&gt;2&lt;/sup&gt; = 87%; N = 185) compared to conventional rehabilitation alone in the short term. Combined MWM and conventional rehabilitation also resulted in improvement in shoulder abduction and external rotation. Compared to Maitland, MWM resulted in improvement in the shoulder abduction MD (20.4°; confidence interval 4.3 to 36.5; I&lt;sup&gt;2&lt;/sup&gt; = 89%; N = 130) in the short term. There is no information regarding long-term effects. Evidence suggests that MWM may reduce shoulder pain and restore shoulder range of motion and function. Our findings are promising, but the evidence is not strong enough to recommend it pragmatically.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Dias Daniela, Neto Mansueto Gomes, Sales Stephane da Silva Ribeiro, Cavalcante Bárbara Dos Santos, Torrierri Palmiro, Roever Leonardo, Araújo Roberto Paulo Correia de</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Journal of clinical medicine</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/38068468</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>37835075</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Disabled People or Their Support Persons' Perceptions of a Community Based Multi-Sensory Environment (MSE): A Mixed-Method Study.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Multi-sensory environments (MSEs) are specialised spaces purposely designed to stimulate the senses, whilst providing a calming and relaxing environment for leisure and enjoyment, predominantly intended for disabled people. Most MSEs are in institutions, hospitals, or educational settings, with a few in community-based settings. We explored disabled users' experiences of a community based MSE in a large metropolitan area in New Zealand, with a view to expanding access to MSE-type environments within the area. We used a convergent mixed method design with a web-based electronic survey (e-survey; &lt;i&gt;n&lt;/i&gt; = 105), as well as semi-structured interviews (&lt;i&gt;n&lt;/i&gt; = 14) with disabled MSE users (adults and children), who were supported, where necessary, by their support person/s. We collected the MSE users' demographics, frequency of use with respect to age, disability, and ethnicity, and experiences of the room, equipment, and accessibility. The participants and their support persons' perspectives about their experiences of using the MSE were represented by four themes: (i) Self-determination; (ii) Enhancing wellbeing opportunities; (iii) the MSE itself; (iv) Accessibility. While the MSE was considered positively, the MSE experience could be enhanced by addressing access challenges and broadening the scope of equipment to improve the usability and make it a more inclusive environment for all.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Wilkinson Amanda, Calder Allyson, Elliott Beth, Rodger Ryan, Mulligan Hilda, Hale Leigh, Perry Meredith</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>International journal of environmental research and public health</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Adult, Child, Humans, Persons with Disabilities, Social Environment, Environment, Leisure Activities, Surveys and Questionnaires</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pubmed/37835075</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
         </is>
       </c>
     </row>
